--- a/URIARTE 630/Mayo/EXPENSAS-MAYO.xlsx
+++ b/URIARTE 630/Mayo/EXPENSAS-MAYO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\URIARTE 630\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B910E393-EA7E-496A-A539-469EE43778AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EDCD65-2804-4DBD-A5EC-1090DB369926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="72">
   <si>
     <t>UF</t>
   </si>
@@ -237,6 +237,9 @@
   </si>
   <si>
     <t>Liquidacion mes de MAYO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERRETERIA V&amp;A </t>
   </si>
 </sst>
 </file>
@@ -1130,6 +1133,8 @@
     <xf numFmtId="3" fontId="1" fillId="3" borderId="46" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="3" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1142,6 +1147,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1159,17 +1173,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1607,10 +1610,10 @@
       <c r="B11" s="19"/>
       <c r="C11" s="20"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="114" t="s">
+      <c r="E11" s="116" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="114"/>
+      <c r="F11" s="116"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="48" t="s">
@@ -1634,7 +1637,7 @@
         <v>44</v>
       </c>
       <c r="B13" s="48"/>
-      <c r="C13" s="132">
+      <c r="C13" s="114">
         <v>3567.21</v>
       </c>
       <c r="D13" s="4"/>
@@ -1658,8 +1661,10 @@
         <v>452681.02959999989</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="58"/>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="58" t="s">
+        <v>71</v>
+      </c>
       <c r="B15" s="48"/>
       <c r="C15" s="46"/>
       <c r="D15" s="24"/>
@@ -1671,7 +1676,7 @@
         <v>62</v>
       </c>
       <c r="B16" s="48"/>
-      <c r="C16" s="133">
+      <c r="C16" s="115">
         <v>109718</v>
       </c>
       <c r="D16" s="24"/>
@@ -1712,7 +1717,7 @@
         <v>39</v>
       </c>
       <c r="B19" s="58"/>
-      <c r="C19" s="132">
+      <c r="C19" s="114">
         <v>142149.12</v>
       </c>
       <c r="E19" s="33"/>
@@ -1863,8 +1868,8 @@
       <c r="F35" s="5"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="115"/>
-      <c r="B36" s="115"/>
+      <c r="A36" s="117"/>
+      <c r="B36" s="117"/>
       <c r="C36" s="88"/>
       <c r="F36" s="5"/>
     </row>
@@ -2008,12 +2013,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="129" t="str">
+      <c r="A1" s="122" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de MAYO</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
       <c r="D1" s="96"/>
       <c r="E1" s="97" t="s">
         <v>36</v>
@@ -2402,48 +2407,48 @@
       </c>
     </row>
     <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="131"/>
-      <c r="B11" s="131"/>
-      <c r="C11" s="131"/>
-      <c r="D11" s="131"/>
-      <c r="E11" s="131"/>
-      <c r="F11" s="131"/>
-      <c r="G11" s="131"/>
-      <c r="H11" s="131"/>
-      <c r="I11" s="131"/>
-      <c r="J11" s="131"/>
-      <c r="K11" s="131"/>
-      <c r="L11" s="131"/>
-      <c r="M11" s="131"/>
+      <c r="A11" s="124"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="124"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="124"/>
+      <c r="I11" s="124"/>
+      <c r="J11" s="124"/>
+      <c r="K11" s="124"/>
+      <c r="L11" s="124"/>
+      <c r="M11" s="124"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="M12" s="5"/>
     </row>
     <row r="13" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="14" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C14" s="120" t="s">
+      <c r="C14" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="121"/>
-      <c r="E14" s="121"/>
-      <c r="F14" s="121"/>
-      <c r="G14" s="121"/>
-      <c r="H14" s="121"/>
-      <c r="I14" s="119"/>
+      <c r="D14" s="126"/>
+      <c r="E14" s="126"/>
+      <c r="F14" s="126"/>
+      <c r="G14" s="126"/>
+      <c r="H14" s="126"/>
+      <c r="I14" s="121"/>
       <c r="J14" s="63"/>
       <c r="K14" s="64"/>
       <c r="L14" s="68"/>
     </row>
     <row r="15" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C15" s="122" t="s">
+      <c r="C15" s="127" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="121"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="121"/>
-      <c r="G15" s="121"/>
-      <c r="H15" s="121"/>
-      <c r="I15" s="119"/>
+      <c r="D15" s="126"/>
+      <c r="E15" s="126"/>
+      <c r="F15" s="126"/>
+      <c r="G15" s="126"/>
+      <c r="H15" s="126"/>
+      <c r="I15" s="121"/>
       <c r="J15" s="65"/>
       <c r="K15" s="66"/>
       <c r="L15" s="68"/>
@@ -2515,15 +2520,15 @@
       </c>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C19" s="123" t="s">
+      <c r="C19" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="124"/>
-      <c r="E19" s="124"/>
-      <c r="F19" s="124"/>
-      <c r="G19" s="124"/>
-      <c r="H19" s="124"/>
-      <c r="I19" s="125"/>
+      <c r="D19" s="129"/>
+      <c r="E19" s="129"/>
+      <c r="F19" s="129"/>
+      <c r="G19" s="129"/>
+      <c r="H19" s="129"/>
+      <c r="I19" s="130"/>
       <c r="J19" s="65"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
@@ -2561,10 +2566,10 @@
       </c>
       <c r="H21" s="72"/>
       <c r="I21" s="66"/>
-      <c r="J21" s="126" t="s">
+      <c r="J21" s="131" t="s">
         <v>53</v>
       </c>
-      <c r="K21" s="127"/>
+      <c r="K21" s="132"/>
       <c r="L21" s="82"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.3">
@@ -2594,8 +2599,8 @@
       <c r="G23" s="68"/>
       <c r="H23" s="68"/>
       <c r="I23" s="66"/>
-      <c r="J23" s="128"/>
-      <c r="K23" s="127"/>
+      <c r="J23" s="133"/>
+      <c r="K23" s="132"/>
       <c r="L23" s="82"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.3">
@@ -2724,47 +2729,47 @@
       <c r="L31" s="68"/>
     </row>
     <row r="32" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="116" t="s">
+      <c r="C32" s="118" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="117"/>
-      <c r="E32" s="117"/>
-      <c r="F32" s="117"/>
-      <c r="G32" s="117"/>
-      <c r="H32" s="118">
+      <c r="D32" s="119"/>
+      <c r="E32" s="119"/>
+      <c r="F32" s="119"/>
+      <c r="G32" s="119"/>
+      <c r="H32" s="120">
         <f>SUM(H24:H31)</f>
         <v>116058.8285</v>
       </c>
-      <c r="I32" s="119"/>
+      <c r="I32" s="121"/>
       <c r="J32" s="76"/>
       <c r="K32" s="77"/>
       <c r="L32" s="68"/>
     </row>
     <row r="35" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="36" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C36" s="120" t="s">
+      <c r="C36" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="D36" s="121"/>
-      <c r="E36" s="121"/>
-      <c r="F36" s="121"/>
-      <c r="G36" s="121"/>
-      <c r="H36" s="121"/>
-      <c r="I36" s="119"/>
+      <c r="D36" s="126"/>
+      <c r="E36" s="126"/>
+      <c r="F36" s="126"/>
+      <c r="G36" s="126"/>
+      <c r="H36" s="126"/>
+      <c r="I36" s="121"/>
       <c r="J36" s="63"/>
       <c r="K36" s="64"/>
       <c r="L36" s="68"/>
     </row>
     <row r="37" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C37" s="122" t="s">
+      <c r="C37" s="127" t="s">
         <v>48</v>
       </c>
-      <c r="D37" s="121"/>
-      <c r="E37" s="121"/>
-      <c r="F37" s="121"/>
-      <c r="G37" s="121"/>
-      <c r="H37" s="121"/>
-      <c r="I37" s="119"/>
+      <c r="D37" s="126"/>
+      <c r="E37" s="126"/>
+      <c r="F37" s="126"/>
+      <c r="G37" s="126"/>
+      <c r="H37" s="126"/>
+      <c r="I37" s="121"/>
       <c r="J37" s="65"/>
       <c r="K37" s="66"/>
       <c r="L37" s="68"/>
@@ -2813,15 +2818,15 @@
       <c r="L40" s="68"/>
     </row>
     <row r="41" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C41" s="123" t="s">
+      <c r="C41" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="D41" s="124"/>
-      <c r="E41" s="124"/>
-      <c r="F41" s="124"/>
-      <c r="G41" s="124"/>
-      <c r="H41" s="124"/>
-      <c r="I41" s="125"/>
+      <c r="D41" s="129"/>
+      <c r="E41" s="129"/>
+      <c r="F41" s="129"/>
+      <c r="G41" s="129"/>
+      <c r="H41" s="129"/>
+      <c r="I41" s="130"/>
       <c r="J41" s="65"/>
       <c r="K41" s="66"/>
       <c r="L41" s="68"/>
@@ -2853,10 +2858,10 @@
       </c>
       <c r="H43" s="72"/>
       <c r="I43" s="66"/>
-      <c r="J43" s="126" t="s">
+      <c r="J43" s="131" t="s">
         <v>53</v>
       </c>
-      <c r="K43" s="127"/>
+      <c r="K43" s="132"/>
       <c r="L43" s="82"/>
     </row>
     <row r="44" spans="3:12" x14ac:dyDescent="0.3">
@@ -2886,8 +2891,8 @@
       <c r="G45" s="68"/>
       <c r="H45" s="68"/>
       <c r="I45" s="66"/>
-      <c r="J45" s="128"/>
-      <c r="K45" s="127"/>
+      <c r="J45" s="133"/>
+      <c r="K45" s="132"/>
       <c r="L45" s="82"/>
     </row>
     <row r="46" spans="3:12" x14ac:dyDescent="0.3">
@@ -2932,47 +2937,47 @@
       <c r="L48" s="68"/>
     </row>
     <row r="49" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C49" s="116" t="s">
+      <c r="C49" s="118" t="s">
         <v>56</v>
       </c>
-      <c r="D49" s="117"/>
-      <c r="E49" s="117"/>
-      <c r="F49" s="117"/>
-      <c r="G49" s="117"/>
-      <c r="H49" s="118">
+      <c r="D49" s="119"/>
+      <c r="E49" s="119"/>
+      <c r="F49" s="119"/>
+      <c r="G49" s="119"/>
+      <c r="H49" s="120">
         <f>M6</f>
         <v>59840.291869695997</v>
       </c>
-      <c r="I49" s="119"/>
+      <c r="I49" s="121"/>
       <c r="J49" s="76"/>
       <c r="K49" s="77"/>
       <c r="L49" s="68"/>
     </row>
     <row r="51" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="52" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C52" s="120" t="s">
+      <c r="C52" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="D52" s="121"/>
-      <c r="E52" s="121"/>
-      <c r="F52" s="121"/>
-      <c r="G52" s="121"/>
-      <c r="H52" s="121"/>
-      <c r="I52" s="119"/>
+      <c r="D52" s="126"/>
+      <c r="E52" s="126"/>
+      <c r="F52" s="126"/>
+      <c r="G52" s="126"/>
+      <c r="H52" s="126"/>
+      <c r="I52" s="121"/>
       <c r="J52" s="63"/>
       <c r="K52" s="64"/>
       <c r="L52" s="68"/>
     </row>
     <row r="53" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C53" s="122" t="s">
+      <c r="C53" s="127" t="s">
         <v>48</v>
       </c>
-      <c r="D53" s="121"/>
-      <c r="E53" s="121"/>
-      <c r="F53" s="121"/>
-      <c r="G53" s="121"/>
-      <c r="H53" s="121"/>
-      <c r="I53" s="119"/>
+      <c r="D53" s="126"/>
+      <c r="E53" s="126"/>
+      <c r="F53" s="126"/>
+      <c r="G53" s="126"/>
+      <c r="H53" s="126"/>
+      <c r="I53" s="121"/>
       <c r="J53" s="65"/>
       <c r="K53" s="66"/>
       <c r="L53" s="68"/>
@@ -3021,15 +3026,15 @@
       <c r="L56" s="68"/>
     </row>
     <row r="57" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C57" s="123" t="s">
+      <c r="C57" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="124"/>
-      <c r="E57" s="124"/>
-      <c r="F57" s="124"/>
-      <c r="G57" s="124"/>
-      <c r="H57" s="124"/>
-      <c r="I57" s="125"/>
+      <c r="D57" s="129"/>
+      <c r="E57" s="129"/>
+      <c r="F57" s="129"/>
+      <c r="G57" s="129"/>
+      <c r="H57" s="129"/>
+      <c r="I57" s="130"/>
       <c r="J57" s="65"/>
       <c r="K57" s="66"/>
       <c r="L57" s="68"/>
@@ -3061,10 +3066,10 @@
       </c>
       <c r="H59" s="72"/>
       <c r="I59" s="66"/>
-      <c r="J59" s="126" t="s">
+      <c r="J59" s="131" t="s">
         <v>53</v>
       </c>
-      <c r="K59" s="127"/>
+      <c r="K59" s="132"/>
       <c r="L59" s="82"/>
     </row>
     <row r="60" spans="3:12" x14ac:dyDescent="0.3">
@@ -3094,8 +3099,8 @@
       <c r="G61" s="68"/>
       <c r="H61" s="68"/>
       <c r="I61" s="66"/>
-      <c r="J61" s="128"/>
-      <c r="K61" s="127"/>
+      <c r="J61" s="133"/>
+      <c r="K61" s="132"/>
       <c r="L61" s="82"/>
     </row>
     <row r="62" spans="3:12" x14ac:dyDescent="0.3">
@@ -3248,47 +3253,47 @@
       <c r="L71" s="68"/>
     </row>
     <row r="72" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C72" s="116" t="s">
+      <c r="C72" s="118" t="s">
         <v>56</v>
       </c>
-      <c r="D72" s="117"/>
-      <c r="E72" s="117"/>
-      <c r="F72" s="117"/>
-      <c r="G72" s="117"/>
-      <c r="H72" s="118">
+      <c r="D72" s="119"/>
+      <c r="E72" s="119"/>
+      <c r="F72" s="119"/>
+      <c r="G72" s="119"/>
+      <c r="H72" s="120">
         <f>SUM(H62:H71)</f>
         <v>116058.8285</v>
       </c>
-      <c r="I72" s="119"/>
+      <c r="I72" s="121"/>
       <c r="J72" s="76"/>
       <c r="K72" s="77"/>
       <c r="L72" s="68"/>
     </row>
     <row r="75" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="76" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C76" s="120" t="s">
+      <c r="C76" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="D76" s="121"/>
-      <c r="E76" s="121"/>
-      <c r="F76" s="121"/>
-      <c r="G76" s="121"/>
-      <c r="H76" s="121"/>
-      <c r="I76" s="119"/>
+      <c r="D76" s="126"/>
+      <c r="E76" s="126"/>
+      <c r="F76" s="126"/>
+      <c r="G76" s="126"/>
+      <c r="H76" s="126"/>
+      <c r="I76" s="121"/>
       <c r="J76" s="63"/>
       <c r="K76" s="64"/>
       <c r="L76" s="68"/>
     </row>
     <row r="77" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C77" s="122" t="s">
+      <c r="C77" s="127" t="s">
         <v>48</v>
       </c>
-      <c r="D77" s="121"/>
-      <c r="E77" s="121"/>
-      <c r="F77" s="121"/>
-      <c r="G77" s="121"/>
-      <c r="H77" s="121"/>
-      <c r="I77" s="119"/>
+      <c r="D77" s="126"/>
+      <c r="E77" s="126"/>
+      <c r="F77" s="126"/>
+      <c r="G77" s="126"/>
+      <c r="H77" s="126"/>
+      <c r="I77" s="121"/>
       <c r="J77" s="65"/>
       <c r="K77" s="66"/>
       <c r="L77" s="68"/>
@@ -3337,15 +3342,15 @@
       <c r="L80" s="68"/>
     </row>
     <row r="81" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C81" s="123" t="s">
+      <c r="C81" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="D81" s="124"/>
-      <c r="E81" s="124"/>
-      <c r="F81" s="124"/>
-      <c r="G81" s="124"/>
-      <c r="H81" s="124"/>
-      <c r="I81" s="125"/>
+      <c r="D81" s="129"/>
+      <c r="E81" s="129"/>
+      <c r="F81" s="129"/>
+      <c r="G81" s="129"/>
+      <c r="H81" s="129"/>
+      <c r="I81" s="130"/>
       <c r="J81" s="65"/>
       <c r="K81" s="66"/>
       <c r="L81" s="68"/>
@@ -3377,10 +3382,10 @@
       </c>
       <c r="H83" s="72"/>
       <c r="I83" s="66"/>
-      <c r="J83" s="126" t="s">
+      <c r="J83" s="131" t="s">
         <v>53</v>
       </c>
-      <c r="K83" s="127"/>
+      <c r="K83" s="132"/>
       <c r="L83" s="82"/>
     </row>
     <row r="84" spans="3:12" x14ac:dyDescent="0.3">
@@ -3410,8 +3415,8 @@
       <c r="G85" s="68"/>
       <c r="H85" s="68"/>
       <c r="I85" s="66"/>
-      <c r="J85" s="128"/>
-      <c r="K85" s="127"/>
+      <c r="J85" s="133"/>
+      <c r="K85" s="132"/>
       <c r="L85" s="82"/>
     </row>
     <row r="86" spans="3:12" x14ac:dyDescent="0.3">
@@ -3539,47 +3544,47 @@
       <c r="L93" s="68"/>
     </row>
     <row r="94" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C94" s="116" t="s">
+      <c r="C94" s="118" t="s">
         <v>56</v>
       </c>
-      <c r="D94" s="117"/>
-      <c r="E94" s="117"/>
-      <c r="F94" s="117"/>
-      <c r="G94" s="117"/>
-      <c r="H94" s="118">
+      <c r="D94" s="119"/>
+      <c r="E94" s="119"/>
+      <c r="F94" s="119"/>
+      <c r="G94" s="119"/>
+      <c r="H94" s="120">
         <f>SUM(H86:H93)</f>
         <v>116058.8285</v>
       </c>
-      <c r="I94" s="119"/>
+      <c r="I94" s="121"/>
       <c r="J94" s="76"/>
       <c r="K94" s="77"/>
       <c r="L94" s="68"/>
     </row>
     <row r="97" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="98" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C98" s="120" t="s">
+      <c r="C98" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="D98" s="121"/>
-      <c r="E98" s="121"/>
-      <c r="F98" s="121"/>
-      <c r="G98" s="121"/>
-      <c r="H98" s="121"/>
-      <c r="I98" s="119"/>
+      <c r="D98" s="126"/>
+      <c r="E98" s="126"/>
+      <c r="F98" s="126"/>
+      <c r="G98" s="126"/>
+      <c r="H98" s="126"/>
+      <c r="I98" s="121"/>
       <c r="J98" s="63"/>
       <c r="K98" s="64"/>
       <c r="L98" s="68"/>
     </row>
     <row r="99" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C99" s="122" t="s">
+      <c r="C99" s="127" t="s">
         <v>48</v>
       </c>
-      <c r="D99" s="121"/>
-      <c r="E99" s="121"/>
-      <c r="F99" s="121"/>
-      <c r="G99" s="121"/>
-      <c r="H99" s="121"/>
-      <c r="I99" s="119"/>
+      <c r="D99" s="126"/>
+      <c r="E99" s="126"/>
+      <c r="F99" s="126"/>
+      <c r="G99" s="126"/>
+      <c r="H99" s="126"/>
+      <c r="I99" s="121"/>
       <c r="J99" s="65"/>
       <c r="K99" s="66"/>
       <c r="L99" s="68"/>
@@ -3628,15 +3633,15 @@
       <c r="L102" s="68"/>
     </row>
     <row r="103" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C103" s="123" t="s">
+      <c r="C103" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="D103" s="124"/>
-      <c r="E103" s="124"/>
-      <c r="F103" s="124"/>
-      <c r="G103" s="124"/>
-      <c r="H103" s="124"/>
-      <c r="I103" s="125"/>
+      <c r="D103" s="129"/>
+      <c r="E103" s="129"/>
+      <c r="F103" s="129"/>
+      <c r="G103" s="129"/>
+      <c r="H103" s="129"/>
+      <c r="I103" s="130"/>
       <c r="J103" s="65"/>
       <c r="K103" s="66"/>
       <c r="L103" s="68"/>
@@ -3668,10 +3673,10 @@
       </c>
       <c r="H105" s="72"/>
       <c r="I105" s="66"/>
-      <c r="J105" s="126" t="s">
+      <c r="J105" s="131" t="s">
         <v>53</v>
       </c>
-      <c r="K105" s="127"/>
+      <c r="K105" s="132"/>
       <c r="L105" s="82"/>
     </row>
     <row r="106" spans="3:12" x14ac:dyDescent="0.3">
@@ -3700,8 +3705,8 @@
       <c r="G107" s="68"/>
       <c r="H107" s="68"/>
       <c r="I107" s="66"/>
-      <c r="J107" s="128"/>
-      <c r="K107" s="127"/>
+      <c r="J107" s="133"/>
+      <c r="K107" s="132"/>
       <c r="L107" s="82"/>
     </row>
     <row r="108" spans="3:12" x14ac:dyDescent="0.3">
@@ -3829,24 +3834,45 @@
       <c r="L115" s="68"/>
     </row>
     <row r="116" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C116" s="116" t="s">
+      <c r="C116" s="118" t="s">
         <v>56</v>
       </c>
-      <c r="D116" s="117"/>
-      <c r="E116" s="117"/>
-      <c r="F116" s="117"/>
-      <c r="G116" s="117"/>
-      <c r="H116" s="118">
+      <c r="D116" s="119"/>
+      <c r="E116" s="119"/>
+      <c r="F116" s="119"/>
+      <c r="G116" s="119"/>
+      <c r="H116" s="120">
         <f>SUM(H108:H115)</f>
         <v>116058.8285</v>
       </c>
-      <c r="I116" s="119"/>
+      <c r="I116" s="121"/>
       <c r="J116" s="76"/>
       <c r="K116" s="77"/>
       <c r="L116" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="C52:I52"/>
+    <mergeCell ref="C53:I53"/>
+    <mergeCell ref="C57:I57"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="J107:K107"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="H94:I94"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="C98:I98"/>
+    <mergeCell ref="C99:I99"/>
+    <mergeCell ref="C103:I103"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C77:I77"/>
+    <mergeCell ref="C81:I81"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="J85:K85"/>
     <mergeCell ref="C116:G116"/>
     <mergeCell ref="H116:I116"/>
     <mergeCell ref="A1:C1"/>
@@ -3863,27 +3889,6 @@
     <mergeCell ref="C41:I41"/>
     <mergeCell ref="J43:K43"/>
     <mergeCell ref="J45:K45"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="J107:K107"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="H94:I94"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="J61:K61"/>
-    <mergeCell ref="C98:I98"/>
-    <mergeCell ref="C99:I99"/>
-    <mergeCell ref="C103:I103"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C77:I77"/>
-    <mergeCell ref="C81:I81"/>
-    <mergeCell ref="J83:K83"/>
-    <mergeCell ref="J85:K85"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="C52:I52"/>
-    <mergeCell ref="C53:I53"/>
-    <mergeCell ref="C57:I57"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/URIARTE 630/Mayo/EXPENSAS-MAYO.xlsx
+++ b/URIARTE 630/Mayo/EXPENSAS-MAYO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\URIARTE 630\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\URIARTE 630\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EDCD65-2804-4DBD-A5EC-1090DB369926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F97FB5-9351-45A6-A333-749F51CBBD01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -253,7 +253,7 @@
     <numFmt numFmtId="167" formatCode="d/m"/>
     <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -338,14 +338,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="0" tint="-0.14999847407452621"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -376,7 +368,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -425,8 +417,14 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="47">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -970,6 +968,56 @@
         <color indexed="64"/>
       </top>
       <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1050,10 +1098,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1064,27 +1108,26 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -1107,8 +1150,6 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="42" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1132,21 +1173,37 @@
     <xf numFmtId="164" fontId="1" fillId="3" borderId="46" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="46" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="3" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="14" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="13" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1156,23 +1213,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="47" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1540,43 +1596,43 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:G69"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:G65"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="16"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="19"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>37</v>
       </c>
@@ -1586,11 +1642,11 @@
       <c r="E7" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="F7" s="57" t="s">
+      <c r="F7" s="55" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1598,97 +1654,99 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="20"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="116" t="s">
+      <c r="E11" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="116"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F11" s="110"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="48" t="s">
         <v>43</v>
       </c>
       <c r="B12" s="48"/>
-      <c r="C12" s="113">
-        <f>62099*5%+62099</f>
-        <v>65203.95</v>
+      <c r="C12" s="108">
+        <f>65200*5%+65200</f>
+        <v>68460</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="31" t="s">
         <v>29</v>
       </c>
       <c r="F12" s="32">
-        <v>-654333.3655716799</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-555114.56597167999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="48" t="s">
         <v>44</v>
       </c>
       <c r="B13" s="48"/>
-      <c r="C13" s="114">
+      <c r="C13" s="108">
         <v>3567.21</v>
       </c>
       <c r="D13" s="4"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="61"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="58" t="s">
+      <c r="E13" s="58"/>
+      <c r="F13" s="59"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="56" t="s">
         <v>57</v>
       </c>
       <c r="B14" s="48"/>
-      <c r="C14" s="46">
+      <c r="C14" s="133">
         <v>82851.100000000006</v>
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="F14" s="81">
+      <c r="F14" s="79">
         <f>'prorrateo '!F10</f>
-        <v>452681.02959999989</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="58" t="s">
+        <v>222681.20490000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="56" t="s">
         <v>71</v>
       </c>
       <c r="B15" s="48"/>
-      <c r="C15" s="46"/>
+      <c r="C15" s="109">
+        <v>20000</v>
+      </c>
       <c r="D15" s="24"/>
       <c r="E15" s="33"/>
-      <c r="F15" s="81"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="58" t="s">
+      <c r="F15" s="79"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="56" t="s">
         <v>62</v>
       </c>
       <c r="B16" s="48"/>
-      <c r="C16" s="115">
+      <c r="C16" s="109">
         <v>109718</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="33"/>
       <c r="F16" s="34"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="58" t="s">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="59"/>
-      <c r="C17" s="113">
+      <c r="B17" s="57"/>
+      <c r="C17" s="133">
         <v>13461.61</v>
       </c>
       <c r="D17" s="4"/>
@@ -1696,50 +1754,50 @@
         <v>19</v>
       </c>
       <c r="F17" s="34">
-        <f>-C41 +C35</f>
-        <v>-448950.99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="58" t="s">
+        <f>-C37 +C31</f>
+        <v>-472207.04</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="56" t="s">
         <v>41</v>
       </c>
       <c r="B18" s="48"/>
-      <c r="C18" s="113">
+      <c r="C18" s="108">
         <v>32000</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="33"/>
       <c r="F18" s="34"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="58" t="s">
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="58"/>
-      <c r="C19" s="114">
+      <c r="B19" s="56"/>
+      <c r="C19" s="108">
         <v>142149.12</v>
       </c>
       <c r="E19" s="33"/>
       <c r="F19" s="34"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="58" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="56" t="s">
         <v>68</v>
       </c>
       <c r="B20" s="48"/>
-      <c r="C20" s="46">
+      <c r="C20" s="133">
         <v>9567.5</v>
       </c>
       <c r="E20" s="33"/>
       <c r="F20" s="34"/>
     </row>
-    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="49"/>
       <c r="B21" s="50"/>
-      <c r="C21" s="84">
+      <c r="C21" s="81">
         <f>SUM(C12:C19)</f>
-        <v>448950.99</v>
+        <v>472207.04</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="35" t="s">
@@ -1747,10 +1805,10 @@
       </c>
       <c r="F21" s="36">
         <f>SUM(F12:F19)</f>
-        <v>-650603.32597167999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>-804640.40107168001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="51" t="s">
         <v>20</v>
       </c>
@@ -1760,223 +1818,191 @@
       <c r="E22" s="12"/>
       <c r="F22" s="13"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="48"/>
       <c r="B23" s="52"/>
-      <c r="C23" s="83"/>
+      <c r="C23" s="9"/>
       <c r="D23" s="4"/>
       <c r="E23" s="12"/>
       <c r="F23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="48"/>
-      <c r="B24" s="52"/>
-      <c r="C24" s="9"/>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="21"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="47">
+        <f>SUM(C22:C23)</f>
+        <v>0</v>
+      </c>
       <c r="D24" s="4"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="13"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="53"/>
-      <c r="B25" s="54"/>
-      <c r="C25" s="83"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="27"/>
+      <c r="C25" s="82">
+        <f>+C24+C21</f>
+        <v>472207.04</v>
+      </c>
       <c r="D25" s="4"/>
       <c r="E25" s="12"/>
       <c r="F25" s="13"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="48"/>
-      <c r="B26" s="52"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="4"/>
+    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="45"/>
+      <c r="C26" s="83"/>
       <c r="E26" s="12"/>
       <c r="F26" s="13"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="48"/>
-      <c r="B27" s="52"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="13"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="21"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="47">
-        <f>SUM(C22:C27)</f>
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="25"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="84"/>
+      <c r="F28" s="5"/>
+    </row>
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="29"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="85">
         <v>0</v>
       </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="5"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="85">
-        <f>+C28+C21</f>
-        <v>448950.99</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="13"/>
-    </row>
-    <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" s="45"/>
-      <c r="C30" s="86"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="13"/>
-    </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="25"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="87"/>
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="37"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="85">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="43"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="86"/>
+      <c r="F31" s="5"/>
+    </row>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="111"/>
+      <c r="B32" s="111"/>
+      <c r="C32" s="85"/>
       <c r="F32" s="5"/>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="29"/>
       <c r="B33" s="28"/>
-      <c r="C33" s="88">
+      <c r="C33" s="85">
         <v>0</v>
       </c>
       <c r="F33" s="5"/>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="37"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="88">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="40"/>
+      <c r="C34" s="54">
+        <f>SUM(C29:C33)</f>
         <v>0</v>
       </c>
-      <c r="F34" s="5"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="43"/>
-      <c r="B35" s="44"/>
-      <c r="C35" s="89"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C35" s="85"/>
       <c r="F35" s="5"/>
     </row>
-    <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="117"/>
-      <c r="B36" s="117"/>
-      <c r="C36" s="88"/>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="87">
+        <f>C35+C25</f>
+        <v>472207.04</v>
+      </c>
       <c r="F36" s="5"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="29"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="88">
-        <v>0</v>
-      </c>
-      <c r="F37" s="5"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="B38" s="40"/>
-      <c r="C38" s="56">
-        <f>SUM(C33:C37)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C39" s="88"/>
-      <c r="F39" s="5"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C40" s="90">
-        <f>C39+C29</f>
-        <v>448950.99</v>
-      </c>
-      <c r="F40" s="5"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="39" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="40"/>
-      <c r="C41" s="56">
-        <f>+C29+C38</f>
-        <v>448950.99</v>
-      </c>
-      <c r="E41" s="10"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D46" s="5"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D49" s="10"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D50" s="10"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="12"/>
+      <c r="B37" s="40"/>
+      <c r="C37" s="54">
+        <f>+C25+C34</f>
+        <v>472207.04</v>
+      </c>
+      <c r="E37" s="10"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D42" s="5"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D45" s="10"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D46" s="10"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="12"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="13"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="11"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="11"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="11"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="11"/>
       <c r="B62" s="11"/>
-      <c r="C62" s="13"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C62" s="11"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="11"/>
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="11"/>
       <c r="B64" s="11"/>
       <c r="C64" s="11"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="11"/>
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="11"/>
-      <c r="B66" s="11"/>
-      <c r="C66" s="11"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="11"/>
-      <c r="B67" s="11"/>
-      <c r="C67" s="11"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="11"/>
-      <c r="B68" s="11"/>
-      <c r="C68" s="11"/>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="11"/>
-      <c r="B69" s="11"/>
-      <c r="C69" s="11"/>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A32:B32"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -1994,57 +2020,55 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T116"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="25.33203125" customWidth="1"/>
-    <col min="4" max="4" width="6.88671875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" customWidth="1"/>
-    <col min="8" max="8" width="0.109375" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="14"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" customWidth="1"/>
+    <col min="8" max="8" width="0.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="122" t="str">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="125" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de MAYO</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="97" t="s">
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="96"/>
-      <c r="G1" s="97" t="s">
+      <c r="F1" s="93"/>
+      <c r="G1" s="128" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="98">
-        <v>84295.42</v>
-      </c>
-      <c r="L1" s="98"/>
-      <c r="M1" s="99">
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="131">
         <v>353462.23</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" s="100" t="str">
+      <c r="M1" s="132"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="95" t="str">
         <f>'detalle y gastos'!F7</f>
         <v>Vto. 16/06</v>
       </c>
-      <c r="B2" s="91"/>
-      <c r="C2" s="91"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
       <c r="D2" s="50"/>
       <c r="E2" s="49"/>
       <c r="F2" s="50"/>
@@ -2054,12 +2078,12 @@
       <c r="H2" s="50"/>
       <c r="I2" s="50"/>
       <c r="J2" s="50"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="101"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="102" t="s">
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="96"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="97" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -2095,12 +2119,12 @@
       <c r="L3" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="M3" s="103" t="s">
+      <c r="M3" s="98" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="102"/>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="97"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
         <v>42</v>
@@ -2115,7 +2139,7 @@
         <v>32</v>
       </c>
       <c r="G4" s="6"/>
-      <c r="H4" s="92">
+      <c r="H4" s="89">
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="I4" s="6" t="s">
@@ -2127,16 +2151,16 @@
       <c r="K4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="93" t="str">
+      <c r="L4" s="90" t="str">
         <f>A2</f>
         <v>Vto. 16/06</v>
       </c>
-      <c r="M4" s="103" t="s">
+      <c r="M4" s="98" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="102">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="97">
         <v>1</v>
       </c>
       <c r="B5" s="7">
@@ -2145,21 +2169,21 @@
       <c r="C5" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="55">
+      <c r="D5" s="53">
         <v>0.5</v>
       </c>
       <c r="E5" s="23">
-        <v>120629.87159999998</v>
+        <v>74227.068299999999</v>
       </c>
       <c r="F5" s="46">
         <f>E5</f>
-        <v>120629.87159999998</v>
-      </c>
-      <c r="G5" s="94">
+        <v>74227.068299999999</v>
+      </c>
+      <c r="G5" s="91">
         <f>E5-F5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="95">
+      <c r="H5" s="92">
         <f>IF(G5&gt;0,G5*8.4%,0)</f>
         <v>0</v>
       </c>
@@ -2167,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="23">
-        <f>M$1*B5</f>
+        <f>L$1*B5</f>
         <v>74227.068299999999</v>
       </c>
       <c r="K5" s="9">
@@ -2178,43 +2202,41 @@
         <f>J5+K5+H5+G5</f>
         <v>74227.068299999999</v>
       </c>
-      <c r="M5" s="104">
+      <c r="M5" s="99">
         <f>L5+L5*4%</f>
         <v>77196.151031999994</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="102">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="97">
         <v>2</v>
       </c>
       <c r="B6" s="7">
         <v>0.16</v>
       </c>
-      <c r="C6" s="62" t="s">
+      <c r="C6" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="55">
+      <c r="D6" s="53">
         <v>0.5</v>
       </c>
       <c r="E6" s="23">
-        <v>91908.473599999998</v>
-      </c>
-      <c r="F6" s="46">
-        <v>91000</v>
-      </c>
-      <c r="G6" s="94">
+        <v>57538.742182399998</v>
+      </c>
+      <c r="F6" s="46"/>
+      <c r="G6" s="91">
         <f t="shared" ref="G6:G9" si="0">E6-F6</f>
-        <v>908.47359999999753</v>
-      </c>
-      <c r="H6" s="95">
+        <v>57538.742182399998</v>
+      </c>
+      <c r="H6" s="92">
         <f t="shared" ref="H6:H9" si="1">IF(G6&gt;0,G6*8.4%,0)</f>
-        <v>76.3117823999998</v>
+        <v>4833.2543433215997</v>
       </c>
       <c r="I6" s="9">
         <v>0</v>
       </c>
       <c r="J6" s="23">
-        <f t="shared" ref="J6:J9" si="2">M$1*B6</f>
+        <f>L$1*B6</f>
         <v>56553.9568</v>
       </c>
       <c r="K6" s="9">
@@ -2222,236 +2244,236 @@
         <v>0</v>
       </c>
       <c r="L6" s="9">
-        <f t="shared" ref="L6:L9" si="3">J6+K6+H6+G6</f>
-        <v>57538.742182399998</v>
-      </c>
-      <c r="M6" s="104">
-        <f t="shared" ref="M6:M9" si="4">L6+L6*4%</f>
-        <v>59840.291869695997</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="102">
+        <f t="shared" ref="L6:L9" si="2">J6+K6+H6+G6</f>
+        <v>118925.9533257216</v>
+      </c>
+      <c r="M6" s="99">
+        <f t="shared" ref="M6:M9" si="3">L6+L6*4%</f>
+        <v>123682.99145875046</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="97">
         <v>3</v>
       </c>
       <c r="B7" s="7">
         <v>0.21</v>
       </c>
-      <c r="C7" s="62" t="s">
+      <c r="C7" s="60" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="55"/>
+      <c r="D7" s="53"/>
       <c r="E7" s="23">
-        <v>120629.87159999998</v>
+        <v>204989.84911439999</v>
       </c>
       <c r="F7" s="46"/>
-      <c r="G7" s="94">
+      <c r="G7" s="91">
         <f t="shared" si="0"/>
-        <v>120629.87159999998</v>
-      </c>
-      <c r="H7" s="95">
+        <v>204989.84911439999</v>
+      </c>
+      <c r="H7" s="92">
         <f t="shared" si="1"/>
-        <v>10132.909214399999</v>
+        <v>17219.1473256096</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="23">
+        <f>L$1*B7</f>
+        <v>74227.068299999999</v>
+      </c>
+      <c r="K7" s="9">
+        <v>0</v>
+      </c>
+      <c r="L7" s="9">
+        <f t="shared" si="2"/>
+        <v>296436.06474000961</v>
+      </c>
+      <c r="M7" s="99">
+        <f t="shared" si="3"/>
+        <v>308293.50732961</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" s="97">
+        <v>4</v>
+      </c>
+      <c r="B8" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="53"/>
+      <c r="E8" s="23">
+        <v>74227.068299999999</v>
+      </c>
+      <c r="F8" s="46">
+        <f>E8</f>
+        <v>74227.068299999999</v>
+      </c>
+      <c r="G8" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="92">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="9"/>
+      <c r="J8" s="23">
+        <f>L$1*B8</f>
+        <v>74227.068299999999</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="9">
         <f t="shared" si="2"/>
         <v>74227.068299999999</v>
       </c>
-      <c r="K7" s="9">
-        <v>0</v>
-      </c>
-      <c r="L7" s="9">
+      <c r="M8" s="99">
         <f t="shared" si="3"/>
-        <v>204989.84911439999</v>
-      </c>
-      <c r="M7" s="104">
-        <f t="shared" si="4"/>
-        <v>213189.44307897598</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="102">
-        <v>4</v>
-      </c>
-      <c r="B8" s="7">
+        <v>77196.151031999994</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="97">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7">
         <v>0.21</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="55"/>
-      <c r="E8" s="23">
-        <v>120421.28639999998</v>
-      </c>
-      <c r="F8" s="46">
-        <f>E8</f>
-        <v>120421.28639999998</v>
-      </c>
-      <c r="G8" s="94">
+      <c r="C9" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="53"/>
+      <c r="E9" s="23">
+        <v>74227.068299999999</v>
+      </c>
+      <c r="F9" s="46">
+        <f>E9</f>
+        <v>74227.068299999999</v>
+      </c>
+      <c r="G9" s="91">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H8" s="95">
+      <c r="H9" s="92">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="23">
+      <c r="I9" s="9"/>
+      <c r="J9" s="23">
+        <f>L$1*B9</f>
+        <v>74227.068299999999</v>
+      </c>
+      <c r="K9" s="9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="9">
         <f t="shared" si="2"/>
         <v>74227.068299999999</v>
       </c>
-      <c r="K8" s="9">
-        <v>0</v>
-      </c>
-      <c r="L8" s="9">
+      <c r="M9" s="99">
         <f t="shared" si="3"/>
-        <v>74227.068299999999</v>
-      </c>
-      <c r="M8" s="104">
-        <f t="shared" si="4"/>
         <v>77196.151031999994</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="102">
-        <v>5</v>
-      </c>
-      <c r="B9" s="7">
-        <v>0.21</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="55"/>
-      <c r="E9" s="23">
-        <v>120629.87159999998</v>
-      </c>
-      <c r="F9" s="46">
-        <f>E9</f>
-        <v>120629.87159999998</v>
-      </c>
-      <c r="G9" s="94">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="95">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="23">
-        <f t="shared" si="2"/>
-        <v>74227.068299999999</v>
-      </c>
-      <c r="K9" s="9">
-        <v>0</v>
-      </c>
-      <c r="L9" s="9">
-        <f t="shared" si="3"/>
-        <v>74227.068299999999</v>
-      </c>
-      <c r="M9" s="104">
-        <f t="shared" si="4"/>
-        <v>77196.151031999994</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="105" t="s">
+    <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="106">
+      <c r="B10" s="101">
         <f>SUM(B5:B9)</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="C10" s="107"/>
-      <c r="D10" s="108">
-        <f t="shared" ref="D10:K10" si="5">SUM(D5:D6)</f>
+      <c r="C10" s="102"/>
+      <c r="D10" s="103">
+        <f t="shared" ref="D10:K10" si="4">SUM(D5:D6)</f>
         <v>1</v>
       </c>
-      <c r="E10" s="109">
+      <c r="E10" s="104">
         <f>SUM(E5:E9)</f>
-        <v>574219.37479999987</v>
-      </c>
-      <c r="F10" s="109">
+        <v>485209.79619679996</v>
+      </c>
+      <c r="F10" s="104">
         <f>SUM(F5:F9)</f>
-        <v>452681.02959999989</v>
-      </c>
-      <c r="G10" s="109">
-        <f t="shared" si="5"/>
-        <v>908.47359999999753</v>
-      </c>
-      <c r="H10" s="109">
-        <f t="shared" si="5"/>
-        <v>76.3117823999998</v>
-      </c>
-      <c r="I10" s="110">
-        <f t="shared" si="5"/>
+        <v>222681.20490000001</v>
+      </c>
+      <c r="G10" s="104">
+        <f t="shared" si="4"/>
+        <v>57538.742182399998</v>
+      </c>
+      <c r="H10" s="104">
+        <f t="shared" si="4"/>
+        <v>4833.2543433215997</v>
+      </c>
+      <c r="I10" s="105">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J10" s="111">
+      <c r="J10" s="106">
         <f>SUM(J5:J9)</f>
         <v>353462.23</v>
       </c>
-      <c r="K10" s="111">
-        <f t="shared" si="5"/>
+      <c r="K10" s="106">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L10" s="109">
+      <c r="L10" s="104">
         <f>SUM(L5:L9)</f>
-        <v>485209.79619679996</v>
-      </c>
-      <c r="M10" s="112">
+        <v>638043.22296573129</v>
+      </c>
+      <c r="M10" s="107">
         <f>SUM(M5:M9)</f>
-        <v>504618.1880446719</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="124"/>
-      <c r="B11" s="124"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="124"/>
-      <c r="E11" s="124"/>
-      <c r="F11" s="124"/>
-      <c r="G11" s="124"/>
-      <c r="H11" s="124"/>
-      <c r="I11" s="124"/>
-      <c r="J11" s="124"/>
-      <c r="K11" s="124"/>
-      <c r="L11" s="124"/>
-      <c r="M11" s="124"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+        <v>663564.9518843604</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="127"/>
+      <c r="B11" s="127"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="127"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="127"/>
+      <c r="J11" s="127"/>
+      <c r="K11" s="127"/>
+      <c r="L11" s="127"/>
+      <c r="M11" s="127"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M12" s="5"/>
     </row>
-    <row r="13" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C14" s="125" t="s">
+    <row r="13" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="126"/>
-      <c r="E14" s="126"/>
-      <c r="F14" s="126"/>
-      <c r="G14" s="126"/>
-      <c r="H14" s="126"/>
-      <c r="I14" s="121"/>
-      <c r="J14" s="63"/>
-      <c r="K14" s="64"/>
-      <c r="L14" s="68"/>
-    </row>
-    <row r="15" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C15" s="127" t="s">
+      <c r="D14" s="117"/>
+      <c r="E14" s="117"/>
+      <c r="F14" s="117"/>
+      <c r="G14" s="117"/>
+      <c r="H14" s="117"/>
+      <c r="I14" s="115"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="66"/>
+    </row>
+    <row r="15" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="126"/>
-      <c r="E15" s="126"/>
-      <c r="F15" s="126"/>
-      <c r="G15" s="126"/>
-      <c r="H15" s="126"/>
-      <c r="I15" s="121"/>
-      <c r="J15" s="65"/>
-      <c r="K15" s="66"/>
-      <c r="L15" s="68"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="117"/>
+      <c r="I15" s="115"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="64"/>
+      <c r="L15" s="66"/>
       <c r="R15" t="s">
         <v>40</v>
       </c>
@@ -2459,19 +2481,19 @@
         <v>96550</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="C16" s="63"/>
-      <c r="D16" s="67"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="67"/>
-      <c r="G16" s="68"/>
-      <c r="H16" s="68" t="s">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C16" s="61"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="I16" s="66"/>
-      <c r="J16" s="65"/>
-      <c r="K16" s="66"/>
-      <c r="L16" s="68"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="63"/>
+      <c r="K16" s="64"/>
+      <c r="L16" s="66"/>
       <c r="R16" t="s">
         <v>38</v>
       </c>
@@ -2479,21 +2501,21 @@
         <v>27991.75</v>
       </c>
     </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C17" s="65" t="s">
+    <row r="17" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C17" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="68" t="s">
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="I17" s="66"/>
-      <c r="J17" s="65"/>
-      <c r="K17" s="66"/>
-      <c r="L17" s="68"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="64"/>
+      <c r="L17" s="66"/>
       <c r="R17" t="s">
         <v>41</v>
       </c>
@@ -2501,17 +2523,17 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C18" s="69"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="70"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="65"/>
-      <c r="K18" s="66"/>
-      <c r="L18" s="68"/>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C18" s="67"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="63"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="66"/>
       <c r="R18" t="s">
         <v>39</v>
       </c>
@@ -2519,31 +2541,31 @@
         <v>24923.78</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C19" s="128" t="s">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C19" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="129"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="129"/>
-      <c r="G19" s="129"/>
-      <c r="H19" s="129"/>
-      <c r="I19" s="130"/>
-      <c r="J19" s="65"/>
-      <c r="K19" s="66"/>
-      <c r="L19" s="68"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C20" s="65"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="68"/>
-      <c r="H20" s="68"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="65"/>
-      <c r="K20" s="66"/>
-      <c r="L20" s="68"/>
+      <c r="D19" s="120"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="120"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="121"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="64"/>
+      <c r="L19" s="66"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C20" s="63"/>
+      <c r="D20" s="66"/>
+      <c r="E20" s="66"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="66"/>
+      <c r="H20" s="66"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="63"/>
+      <c r="K20" s="64"/>
+      <c r="L20" s="66"/>
       <c r="R20" t="s">
         <v>45</v>
       </c>
@@ -2551,1312 +2573,1325 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C21" s="65" t="s">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C21" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68" t="str">
+      <c r="D21" s="66"/>
+      <c r="E21" s="66" t="str">
         <f>C5</f>
         <v>TARQUIRINI SABRINA</v>
       </c>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68" t="s">
+      <c r="F21" s="66"/>
+      <c r="G21" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="H21" s="72"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="131" t="s">
+      <c r="H21" s="70"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="122" t="s">
         <v>53</v>
       </c>
-      <c r="K21" s="132"/>
-      <c r="L21" s="82"/>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C22" s="65" t="s">
+      <c r="K21" s="123"/>
+      <c r="L21" s="80"/>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C22" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="73" t="s">
+      <c r="D22" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="68">
+      <c r="E22" s="66">
         <f>A5</f>
         <v>1</v>
       </c>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="65"/>
-      <c r="K22" s="66"/>
-      <c r="L22" s="68"/>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C23" s="65"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="68"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="66"/>
-      <c r="J23" s="133"/>
-      <c r="K23" s="132"/>
-      <c r="L23" s="82"/>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C24" s="79" t="s">
+      <c r="F22" s="66"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="63"/>
+      <c r="K22" s="64"/>
+      <c r="L22" s="66"/>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C23" s="63"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="124"/>
+      <c r="K23" s="123"/>
+      <c r="L23" s="80"/>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C24" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="68"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="68"/>
-      <c r="G24" s="68"/>
-      <c r="H24" s="78">
-        <f>M$1/5</f>
+      <c r="D24" s="66"/>
+      <c r="E24" s="66"/>
+      <c r="F24" s="66"/>
+      <c r="G24" s="66"/>
+      <c r="H24" s="76">
+        <f>L$1/5</f>
         <v>70692.445999999996</v>
       </c>
-      <c r="I24" s="66"/>
-      <c r="J24" s="65"/>
-      <c r="K24" s="66"/>
-      <c r="L24" s="68"/>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C25" s="80" t="s">
+      <c r="I24" s="64"/>
+      <c r="J24" s="63"/>
+      <c r="K24" s="64"/>
+      <c r="L24" s="66"/>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C25" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="78">
+      <c r="D25" s="66"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="76">
         <f>T$15/4</f>
         <v>24137.5</v>
       </c>
-      <c r="I25" s="66"/>
-      <c r="J25" s="65"/>
-      <c r="K25" s="66"/>
-      <c r="L25" s="68"/>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C26" s="80" t="s">
+      <c r="I25" s="64"/>
+      <c r="J25" s="63"/>
+      <c r="K25" s="64"/>
+      <c r="L25" s="66"/>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C26" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="68"/>
-      <c r="E26" s="68"/>
-      <c r="F26" s="68"/>
-      <c r="G26" s="68"/>
-      <c r="H26" s="78">
+      <c r="D26" s="66"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="66"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="76">
         <f>T$16/4</f>
         <v>6997.9375</v>
       </c>
-      <c r="I26" s="66"/>
-      <c r="J26" s="65"/>
-      <c r="K26" s="66"/>
-      <c r="L26" s="68"/>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C27" s="80" t="s">
+      <c r="I26" s="64"/>
+      <c r="J26" s="63"/>
+      <c r="K26" s="64"/>
+      <c r="L26" s="66"/>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C27" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="68"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="68"/>
-      <c r="G27" s="68"/>
-      <c r="H27" s="78">
+      <c r="D27" s="66"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="66"/>
+      <c r="G27" s="66"/>
+      <c r="H27" s="76">
         <f>T$17/4</f>
         <v>8000</v>
       </c>
-      <c r="I27" s="66"/>
-      <c r="J27" s="65"/>
-      <c r="K27" s="66"/>
-      <c r="L27" s="68"/>
-    </row>
-    <row r="28" spans="3:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="80" t="s">
+      <c r="I27" s="64"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="64"/>
+      <c r="L27" s="66"/>
+    </row>
+    <row r="28" spans="3:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="68"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="68"/>
-      <c r="G28" s="68"/>
-      <c r="H28" s="78">
+      <c r="D28" s="66"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="66"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="76">
         <f>T$18/4</f>
         <v>6230.9449999999997</v>
       </c>
-      <c r="I28" s="66"/>
-      <c r="J28" s="65"/>
-      <c r="K28" s="66"/>
-      <c r="L28" s="68"/>
-    </row>
-    <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="D29" s="68"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="68"/>
-      <c r="H29" s="78"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="66"/>
-      <c r="L29" s="68"/>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C30" s="80" t="s">
+      <c r="I28" s="64"/>
+      <c r="J28" s="63"/>
+      <c r="K28" s="64"/>
+      <c r="L28" s="66"/>
+    </row>
+    <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D29" s="66"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="66"/>
+      <c r="G29" s="66"/>
+      <c r="H29" s="76"/>
+      <c r="I29" s="64"/>
+      <c r="J29" s="63"/>
+      <c r="K29" s="64"/>
+      <c r="L29" s="66"/>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C30" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="68"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="68"/>
-      <c r="H30" s="78">
+      <c r="D30" s="66"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="66"/>
+      <c r="G30" s="66"/>
+      <c r="H30" s="76">
         <f>T$20/3</f>
         <v>0</v>
       </c>
-      <c r="I30" s="66"/>
-      <c r="J30" s="65"/>
-      <c r="K30" s="66"/>
-      <c r="L30" s="68"/>
-    </row>
-    <row r="31" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C31" s="65"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="68"/>
-      <c r="G31" s="68"/>
-      <c r="H31" s="68"/>
-      <c r="I31" s="66"/>
-      <c r="J31" s="74"/>
-      <c r="K31" s="75"/>
-      <c r="L31" s="68"/>
-    </row>
-    <row r="32" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="118" t="s">
+      <c r="I30" s="64"/>
+      <c r="J30" s="63"/>
+      <c r="K30" s="64"/>
+      <c r="L30" s="66"/>
+    </row>
+    <row r="31" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C31" s="63"/>
+      <c r="D31" s="66"/>
+      <c r="E31" s="66"/>
+      <c r="F31" s="66"/>
+      <c r="G31" s="66"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="64"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="66"/>
+    </row>
+    <row r="32" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="119"/>
-      <c r="E32" s="119"/>
-      <c r="F32" s="119"/>
-      <c r="G32" s="119"/>
-      <c r="H32" s="120">
+      <c r="D32" s="113"/>
+      <c r="E32" s="113"/>
+      <c r="F32" s="113"/>
+      <c r="G32" s="113"/>
+      <c r="H32" s="114">
         <f>SUM(H24:H31)</f>
         <v>116058.8285</v>
       </c>
-      <c r="I32" s="121"/>
-      <c r="J32" s="76"/>
-      <c r="K32" s="77"/>
-      <c r="L32" s="68"/>
-    </row>
-    <row r="35" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="36" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C36" s="125" t="s">
+      <c r="I32" s="115"/>
+      <c r="J32" s="74"/>
+      <c r="K32" s="75"/>
+      <c r="L32" s="66"/>
+    </row>
+    <row r="35" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="D36" s="126"/>
-      <c r="E36" s="126"/>
-      <c r="F36" s="126"/>
-      <c r="G36" s="126"/>
-      <c r="H36" s="126"/>
-      <c r="I36" s="121"/>
-      <c r="J36" s="63"/>
-      <c r="K36" s="64"/>
-      <c r="L36" s="68"/>
-    </row>
-    <row r="37" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C37" s="127" t="s">
+      <c r="D36" s="117"/>
+      <c r="E36" s="117"/>
+      <c r="F36" s="117"/>
+      <c r="G36" s="117"/>
+      <c r="H36" s="117"/>
+      <c r="I36" s="115"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="62"/>
+      <c r="L36" s="66"/>
+    </row>
+    <row r="37" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="D37" s="126"/>
-      <c r="E37" s="126"/>
-      <c r="F37" s="126"/>
-      <c r="G37" s="126"/>
-      <c r="H37" s="126"/>
-      <c r="I37" s="121"/>
-      <c r="J37" s="65"/>
-      <c r="K37" s="66"/>
-      <c r="L37" s="68"/>
-    </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C38" s="63"/>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="68"/>
-      <c r="H38" s="68" t="s">
+      <c r="D37" s="117"/>
+      <c r="E37" s="117"/>
+      <c r="F37" s="117"/>
+      <c r="G37" s="117"/>
+      <c r="H37" s="117"/>
+      <c r="I37" s="115"/>
+      <c r="J37" s="63"/>
+      <c r="K37" s="64"/>
+      <c r="L37" s="66"/>
+    </row>
+    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C38" s="61"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="I38" s="66"/>
-      <c r="J38" s="65"/>
-      <c r="K38" s="66"/>
-      <c r="L38" s="68"/>
-    </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C39" s="65" t="s">
+      <c r="I38" s="64"/>
+      <c r="J38" s="63"/>
+      <c r="K38" s="64"/>
+      <c r="L38" s="66"/>
+    </row>
+    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C39" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="68"/>
-      <c r="H39" s="68" t="str">
+      <c r="D39" s="66"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="66"/>
+      <c r="H39" s="66" t="str">
         <f>H17</f>
         <v>VENCIMIENTO: DICIEMBRE</v>
       </c>
-      <c r="I39" s="66"/>
-      <c r="J39" s="65"/>
-      <c r="K39" s="66"/>
-      <c r="L39" s="68"/>
-    </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C40" s="69"/>
-      <c r="D40" s="70"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="70"/>
-      <c r="G40" s="70"/>
-      <c r="H40" s="70"/>
-      <c r="I40" s="71"/>
-      <c r="J40" s="65"/>
-      <c r="K40" s="66"/>
-      <c r="L40" s="68"/>
-    </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C41" s="128" t="s">
+      <c r="I39" s="64"/>
+      <c r="J39" s="63"/>
+      <c r="K39" s="64"/>
+      <c r="L39" s="66"/>
+    </row>
+    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C40" s="67"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="68"/>
+      <c r="H40" s="68"/>
+      <c r="I40" s="69"/>
+      <c r="J40" s="63"/>
+      <c r="K40" s="64"/>
+      <c r="L40" s="66"/>
+    </row>
+    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C41" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="D41" s="129"/>
-      <c r="E41" s="129"/>
-      <c r="F41" s="129"/>
-      <c r="G41" s="129"/>
-      <c r="H41" s="129"/>
-      <c r="I41" s="130"/>
-      <c r="J41" s="65"/>
-      <c r="K41" s="66"/>
-      <c r="L41" s="68"/>
-    </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C42" s="65"/>
-      <c r="D42" s="68"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="68"/>
-      <c r="H42" s="68"/>
-      <c r="I42" s="66"/>
-      <c r="J42" s="65"/>
-      <c r="K42" s="66"/>
-      <c r="L42" s="68"/>
-    </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C43" s="65" t="s">
+      <c r="D41" s="120"/>
+      <c r="E41" s="120"/>
+      <c r="F41" s="120"/>
+      <c r="G41" s="120"/>
+      <c r="H41" s="120"/>
+      <c r="I41" s="121"/>
+      <c r="J41" s="63"/>
+      <c r="K41" s="64"/>
+      <c r="L41" s="66"/>
+    </row>
+    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C42" s="63"/>
+      <c r="D42" s="66"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="66"/>
+      <c r="G42" s="66"/>
+      <c r="H42" s="66"/>
+      <c r="I42" s="64"/>
+      <c r="J42" s="63"/>
+      <c r="K42" s="64"/>
+      <c r="L42" s="66"/>
+    </row>
+    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C43" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68" t="str">
+      <c r="D43" s="66"/>
+      <c r="E43" s="66" t="str">
         <f>C7</f>
         <v>LUCA BASUALDO</v>
       </c>
-      <c r="F43" s="68"/>
-      <c r="G43" s="68" t="s">
+      <c r="F43" s="66"/>
+      <c r="G43" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="H43" s="72"/>
-      <c r="I43" s="66"/>
-      <c r="J43" s="131" t="s">
+      <c r="H43" s="70"/>
+      <c r="I43" s="64"/>
+      <c r="J43" s="122" t="s">
         <v>53</v>
       </c>
-      <c r="K43" s="132"/>
-      <c r="L43" s="82"/>
-    </row>
-    <row r="44" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C44" s="65" t="s">
+      <c r="K43" s="123"/>
+      <c r="L43" s="80"/>
+    </row>
+    <row r="44" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C44" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="73" t="s">
+      <c r="D44" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="E44" s="68">
+      <c r="E44" s="66">
         <f>A7</f>
         <v>3</v>
       </c>
-      <c r="F44" s="68"/>
-      <c r="G44" s="68"/>
-      <c r="H44" s="68"/>
-      <c r="I44" s="66"/>
-      <c r="J44" s="65"/>
-      <c r="K44" s="66"/>
-      <c r="L44" s="68"/>
-    </row>
-    <row r="45" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C45" s="65"/>
-      <c r="D45" s="68"/>
-      <c r="E45" s="68"/>
-      <c r="F45" s="68"/>
-      <c r="G45" s="68"/>
-      <c r="H45" s="68"/>
-      <c r="I45" s="66"/>
-      <c r="J45" s="133"/>
-      <c r="K45" s="132"/>
-      <c r="L45" s="82"/>
-    </row>
-    <row r="46" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C46" s="65" t="s">
+      <c r="F44" s="66"/>
+      <c r="G44" s="66"/>
+      <c r="H44" s="66"/>
+      <c r="I44" s="64"/>
+      <c r="J44" s="63"/>
+      <c r="K44" s="64"/>
+      <c r="L44" s="66"/>
+    </row>
+    <row r="45" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C45" s="63"/>
+      <c r="D45" s="66"/>
+      <c r="E45" s="66"/>
+      <c r="F45" s="66"/>
+      <c r="G45" s="66"/>
+      <c r="H45" s="66"/>
+      <c r="I45" s="64"/>
+      <c r="J45" s="124"/>
+      <c r="K45" s="123"/>
+      <c r="L45" s="80"/>
+    </row>
+    <row r="46" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C46" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="D46" s="68"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="68"/>
-      <c r="G46" s="68"/>
-      <c r="H46" s="78">
-        <f>M$1/5</f>
+      <c r="D46" s="66"/>
+      <c r="E46" s="66"/>
+      <c r="F46" s="66"/>
+      <c r="G46" s="66"/>
+      <c r="H46" s="76">
+        <f>L$1/5</f>
         <v>70692.445999999996</v>
       </c>
-      <c r="I46" s="66"/>
-      <c r="J46" s="65"/>
-      <c r="K46" s="66"/>
-      <c r="L46" s="68"/>
-    </row>
-    <row r="47" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C47" s="65"/>
-      <c r="D47" s="68"/>
-      <c r="E47" s="68"/>
-      <c r="F47" s="68"/>
-      <c r="G47" s="68"/>
-      <c r="H47" s="68"/>
-      <c r="I47" s="66"/>
-      <c r="J47" s="65"/>
-      <c r="K47" s="66"/>
-      <c r="L47" s="68"/>
-    </row>
-    <row r="48" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C48" s="65"/>
-      <c r="D48" s="68"/>
-      <c r="E48" s="68"/>
-      <c r="F48" s="68"/>
-      <c r="G48" s="68"/>
-      <c r="H48" s="68"/>
-      <c r="I48" s="66"/>
-      <c r="J48" s="74"/>
-      <c r="K48" s="75"/>
-      <c r="L48" s="68"/>
-    </row>
-    <row r="49" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C49" s="118" t="s">
+      <c r="I46" s="64"/>
+      <c r="J46" s="63"/>
+      <c r="K46" s="64"/>
+      <c r="L46" s="66"/>
+    </row>
+    <row r="47" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C47" s="63"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="64"/>
+      <c r="J47" s="63"/>
+      <c r="K47" s="64"/>
+      <c r="L47" s="66"/>
+    </row>
+    <row r="48" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C48" s="63"/>
+      <c r="D48" s="66"/>
+      <c r="E48" s="66"/>
+      <c r="F48" s="66"/>
+      <c r="G48" s="66"/>
+      <c r="H48" s="66"/>
+      <c r="I48" s="64"/>
+      <c r="J48" s="72"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="66"/>
+    </row>
+    <row r="49" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="D49" s="119"/>
-      <c r="E49" s="119"/>
-      <c r="F49" s="119"/>
-      <c r="G49" s="119"/>
-      <c r="H49" s="120">
+      <c r="D49" s="113"/>
+      <c r="E49" s="113"/>
+      <c r="F49" s="113"/>
+      <c r="G49" s="113"/>
+      <c r="H49" s="114">
         <f>M6</f>
-        <v>59840.291869695997</v>
-      </c>
-      <c r="I49" s="121"/>
-      <c r="J49" s="76"/>
-      <c r="K49" s="77"/>
-      <c r="L49" s="68"/>
-    </row>
-    <row r="51" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="52" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C52" s="125" t="s">
+        <v>123682.99145875046</v>
+      </c>
+      <c r="I49" s="115"/>
+      <c r="J49" s="74"/>
+      <c r="K49" s="75"/>
+      <c r="L49" s="66"/>
+    </row>
+    <row r="51" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C52" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="D52" s="126"/>
-      <c r="E52" s="126"/>
-      <c r="F52" s="126"/>
-      <c r="G52" s="126"/>
-      <c r="H52" s="126"/>
-      <c r="I52" s="121"/>
-      <c r="J52" s="63"/>
-      <c r="K52" s="64"/>
-      <c r="L52" s="68"/>
-    </row>
-    <row r="53" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C53" s="127" t="s">
+      <c r="D52" s="117"/>
+      <c r="E52" s="117"/>
+      <c r="F52" s="117"/>
+      <c r="G52" s="117"/>
+      <c r="H52" s="117"/>
+      <c r="I52" s="115"/>
+      <c r="J52" s="61"/>
+      <c r="K52" s="62"/>
+      <c r="L52" s="66"/>
+    </row>
+    <row r="53" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C53" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="D53" s="126"/>
-      <c r="E53" s="126"/>
-      <c r="F53" s="126"/>
-      <c r="G53" s="126"/>
-      <c r="H53" s="126"/>
-      <c r="I53" s="121"/>
-      <c r="J53" s="65"/>
-      <c r="K53" s="66"/>
-      <c r="L53" s="68"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C54" s="63"/>
-      <c r="D54" s="67"/>
-      <c r="E54" s="67"/>
-      <c r="F54" s="67"/>
-      <c r="G54" s="68"/>
-      <c r="H54" s="68" t="s">
+      <c r="D53" s="117"/>
+      <c r="E53" s="117"/>
+      <c r="F53" s="117"/>
+      <c r="G53" s="117"/>
+      <c r="H53" s="117"/>
+      <c r="I53" s="115"/>
+      <c r="J53" s="63"/>
+      <c r="K53" s="64"/>
+      <c r="L53" s="66"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C54" s="61"/>
+      <c r="D54" s="65"/>
+      <c r="E54" s="65"/>
+      <c r="F54" s="65"/>
+      <c r="G54" s="66"/>
+      <c r="H54" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="I54" s="66"/>
-      <c r="J54" s="65"/>
-      <c r="K54" s="66"/>
-      <c r="L54" s="68"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C55" s="65" t="s">
+      <c r="I54" s="64"/>
+      <c r="J54" s="63"/>
+      <c r="K54" s="64"/>
+      <c r="L54" s="66"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C55" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="D55" s="68"/>
-      <c r="E55" s="68"/>
-      <c r="F55" s="68"/>
-      <c r="G55" s="68"/>
-      <c r="H55" s="68" t="str">
+      <c r="D55" s="66"/>
+      <c r="E55" s="66"/>
+      <c r="F55" s="66"/>
+      <c r="G55" s="66"/>
+      <c r="H55" s="66" t="str">
         <f>H17</f>
         <v>VENCIMIENTO: DICIEMBRE</v>
       </c>
-      <c r="I55" s="66"/>
-      <c r="J55" s="65"/>
-      <c r="K55" s="66"/>
-      <c r="L55" s="68"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C56" s="69"/>
-      <c r="D56" s="70"/>
-      <c r="E56" s="70"/>
-      <c r="F56" s="70"/>
-      <c r="G56" s="70"/>
-      <c r="H56" s="70"/>
-      <c r="I56" s="71"/>
-      <c r="J56" s="65"/>
-      <c r="K56" s="66"/>
-      <c r="L56" s="68"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C57" s="128" t="s">
+      <c r="I55" s="64"/>
+      <c r="J55" s="63"/>
+      <c r="K55" s="64"/>
+      <c r="L55" s="66"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C56" s="67"/>
+      <c r="D56" s="68"/>
+      <c r="E56" s="68"/>
+      <c r="F56" s="68"/>
+      <c r="G56" s="68"/>
+      <c r="H56" s="68"/>
+      <c r="I56" s="69"/>
+      <c r="J56" s="63"/>
+      <c r="K56" s="64"/>
+      <c r="L56" s="66"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C57" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="129"/>
-      <c r="E57" s="129"/>
-      <c r="F57" s="129"/>
-      <c r="G57" s="129"/>
-      <c r="H57" s="129"/>
-      <c r="I57" s="130"/>
-      <c r="J57" s="65"/>
-      <c r="K57" s="66"/>
-      <c r="L57" s="68"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C58" s="65"/>
-      <c r="D58" s="68"/>
-      <c r="E58" s="68"/>
-      <c r="F58" s="68"/>
-      <c r="G58" s="68"/>
-      <c r="H58" s="68"/>
-      <c r="I58" s="66"/>
-      <c r="J58" s="65"/>
-      <c r="K58" s="66"/>
-      <c r="L58" s="68"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C59" s="65" t="s">
+      <c r="D57" s="120"/>
+      <c r="E57" s="120"/>
+      <c r="F57" s="120"/>
+      <c r="G57" s="120"/>
+      <c r="H57" s="120"/>
+      <c r="I57" s="121"/>
+      <c r="J57" s="63"/>
+      <c r="K57" s="64"/>
+      <c r="L57" s="66"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C58" s="63"/>
+      <c r="D58" s="66"/>
+      <c r="E58" s="66"/>
+      <c r="F58" s="66"/>
+      <c r="G58" s="66"/>
+      <c r="H58" s="66"/>
+      <c r="I58" s="64"/>
+      <c r="J58" s="63"/>
+      <c r="K58" s="64"/>
+      <c r="L58" s="66"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C59" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="D59" s="68"/>
-      <c r="E59" s="68" t="str">
+      <c r="D59" s="66"/>
+      <c r="E59" s="66" t="str">
         <f>C6</f>
         <v>CASTILLO JONATHAN</v>
       </c>
-      <c r="F59" s="68"/>
-      <c r="G59" s="68" t="s">
+      <c r="F59" s="66"/>
+      <c r="G59" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="H59" s="72"/>
-      <c r="I59" s="66"/>
-      <c r="J59" s="131" t="s">
+      <c r="H59" s="70"/>
+      <c r="I59" s="64"/>
+      <c r="J59" s="122" t="s">
         <v>53</v>
       </c>
-      <c r="K59" s="132"/>
-      <c r="L59" s="82"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C60" s="65" t="s">
+      <c r="K59" s="123"/>
+      <c r="L59" s="80"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C60" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="D60" s="73" t="s">
+      <c r="D60" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="E60" s="68">
+      <c r="E60" s="66">
         <f>A6</f>
         <v>2</v>
       </c>
-      <c r="F60" s="68"/>
-      <c r="G60" s="68"/>
-      <c r="H60" s="68"/>
-      <c r="I60" s="66"/>
-      <c r="J60" s="65"/>
-      <c r="K60" s="66"/>
-      <c r="L60" s="68"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C61" s="65"/>
-      <c r="D61" s="68"/>
-      <c r="E61" s="68"/>
-      <c r="F61" s="68"/>
-      <c r="G61" s="68"/>
-      <c r="H61" s="68"/>
-      <c r="I61" s="66"/>
-      <c r="J61" s="133"/>
-      <c r="K61" s="132"/>
-      <c r="L61" s="82"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C62" s="65" t="s">
+      <c r="F60" s="66"/>
+      <c r="G60" s="66"/>
+      <c r="H60" s="66"/>
+      <c r="I60" s="64"/>
+      <c r="J60" s="63"/>
+      <c r="K60" s="64"/>
+      <c r="L60" s="66"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C61" s="63"/>
+      <c r="D61" s="66"/>
+      <c r="E61" s="66"/>
+      <c r="F61" s="66"/>
+      <c r="G61" s="66"/>
+      <c r="H61" s="66"/>
+      <c r="I61" s="64"/>
+      <c r="J61" s="124"/>
+      <c r="K61" s="123"/>
+      <c r="L61" s="80"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C62" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="D62" s="68"/>
-      <c r="E62" s="68"/>
-      <c r="F62" s="68"/>
-      <c r="G62" s="68"/>
-      <c r="H62" s="78">
-        <f>M$1/5</f>
+      <c r="D62" s="66"/>
+      <c r="E62" s="66"/>
+      <c r="F62" s="66"/>
+      <c r="G62" s="66"/>
+      <c r="H62" s="76">
+        <f>L$1/5</f>
         <v>70692.445999999996</v>
       </c>
-      <c r="I62" s="66"/>
-      <c r="J62" s="65"/>
-      <c r="K62" s="66"/>
-      <c r="L62" s="68"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C63" s="80" t="s">
+      <c r="I62" s="64"/>
+      <c r="J62" s="63"/>
+      <c r="K62" s="64"/>
+      <c r="L62" s="66"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C63" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="D63" s="68"/>
-      <c r="E63" s="68"/>
-      <c r="F63" s="68"/>
-      <c r="G63" s="68"/>
-      <c r="H63" s="78">
+      <c r="D63" s="66"/>
+      <c r="E63" s="66"/>
+      <c r="F63" s="66"/>
+      <c r="G63" s="66"/>
+      <c r="H63" s="76">
         <f>T$15/4</f>
         <v>24137.5</v>
       </c>
-      <c r="I63" s="66"/>
-      <c r="J63" s="65"/>
-      <c r="K63" s="66"/>
-      <c r="L63" s="68"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C64" s="80" t="s">
+      <c r="I63" s="64"/>
+      <c r="J63" s="63"/>
+      <c r="K63" s="64"/>
+      <c r="L63" s="66"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C64" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="D64" s="68"/>
-      <c r="E64" s="68"/>
-      <c r="F64" s="68"/>
-      <c r="G64" s="68"/>
-      <c r="H64" s="78">
+      <c r="D64" s="66"/>
+      <c r="E64" s="66"/>
+      <c r="F64" s="66"/>
+      <c r="G64" s="66"/>
+      <c r="H64" s="76">
         <f>T$16/4</f>
         <v>6997.9375</v>
       </c>
-      <c r="I64" s="66"/>
-      <c r="J64" s="65"/>
-      <c r="K64" s="66"/>
-      <c r="L64" s="68"/>
-    </row>
-    <row r="65" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C65" s="80" t="s">
+      <c r="I64" s="64"/>
+      <c r="J64" s="63"/>
+      <c r="K64" s="64"/>
+      <c r="L64" s="66"/>
+    </row>
+    <row r="65" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C65" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="D65" s="68"/>
-      <c r="E65" s="68"/>
-      <c r="F65" s="68"/>
-      <c r="G65" s="68"/>
-      <c r="H65" s="78">
+      <c r="D65" s="66"/>
+      <c r="E65" s="66"/>
+      <c r="F65" s="66"/>
+      <c r="G65" s="66"/>
+      <c r="H65" s="76">
         <f>T$17/4</f>
         <v>8000</v>
       </c>
-      <c r="I65" s="66"/>
-      <c r="J65" s="65"/>
-      <c r="K65" s="66"/>
-      <c r="L65" s="68"/>
-    </row>
-    <row r="66" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C66" s="80" t="s">
+      <c r="I65" s="64"/>
+      <c r="J65" s="63"/>
+      <c r="K65" s="64"/>
+      <c r="L65" s="66"/>
+    </row>
+    <row r="66" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C66" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="D66" s="68"/>
-      <c r="E66" s="68"/>
-      <c r="F66" s="68"/>
-      <c r="G66" s="68"/>
-      <c r="H66" s="78">
+      <c r="D66" s="66"/>
+      <c r="E66" s="66"/>
+      <c r="F66" s="66"/>
+      <c r="G66" s="66"/>
+      <c r="H66" s="76">
         <f>T$18/4</f>
         <v>6230.9449999999997</v>
       </c>
-      <c r="I66" s="66"/>
-      <c r="J66" s="65"/>
-      <c r="K66" s="66"/>
-      <c r="L66" s="68"/>
-    </row>
-    <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="D67" s="68"/>
-      <c r="E67" s="68"/>
-      <c r="F67" s="68"/>
-      <c r="G67" s="68"/>
-      <c r="H67" s="78"/>
-      <c r="I67" s="66"/>
-      <c r="J67" s="65"/>
-      <c r="K67" s="66"/>
-      <c r="L67" s="68"/>
-    </row>
-    <row r="68" spans="3:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C68" s="80" t="s">
+      <c r="I66" s="64"/>
+      <c r="J66" s="63"/>
+      <c r="K66" s="64"/>
+      <c r="L66" s="66"/>
+    </row>
+    <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D67" s="66"/>
+      <c r="E67" s="66"/>
+      <c r="F67" s="66"/>
+      <c r="G67" s="66"/>
+      <c r="H67" s="76"/>
+      <c r="I67" s="64"/>
+      <c r="J67" s="63"/>
+      <c r="K67" s="64"/>
+      <c r="L67" s="66"/>
+    </row>
+    <row r="68" spans="3:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C68" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="D68" s="68"/>
-      <c r="E68" s="68"/>
-      <c r="F68" s="68"/>
-      <c r="G68" s="68"/>
-      <c r="H68" s="78">
+      <c r="D68" s="66"/>
+      <c r="E68" s="66"/>
+      <c r="F68" s="66"/>
+      <c r="G68" s="66"/>
+      <c r="H68" s="76">
         <f>T$20/3</f>
         <v>0</v>
       </c>
-      <c r="I68" s="66"/>
-      <c r="J68" s="65"/>
-      <c r="K68" s="66"/>
-      <c r="L68" s="68"/>
-    </row>
-    <row r="69" spans="3:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C69" s="65"/>
-      <c r="D69" s="68"/>
-      <c r="E69" s="68"/>
-      <c r="F69" s="68"/>
-      <c r="G69" s="68"/>
-      <c r="H69" s="68"/>
-      <c r="I69" s="66"/>
-      <c r="J69" s="65"/>
-      <c r="K69" s="66"/>
-      <c r="L69" s="68"/>
-    </row>
-    <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C70" s="65"/>
-      <c r="D70" s="68"/>
-      <c r="E70" s="68"/>
-      <c r="F70" s="68"/>
-      <c r="G70" s="68"/>
-      <c r="H70" s="68"/>
-      <c r="I70" s="66"/>
-      <c r="J70" s="65"/>
-      <c r="K70" s="66"/>
-      <c r="L70" s="68"/>
-    </row>
-    <row r="71" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C71" s="65"/>
-      <c r="D71" s="68"/>
-      <c r="E71" s="68"/>
-      <c r="F71" s="68"/>
-      <c r="G71" s="68"/>
-      <c r="H71" s="68"/>
-      <c r="I71" s="66"/>
-      <c r="J71" s="74"/>
-      <c r="K71" s="75"/>
-      <c r="L71" s="68"/>
-    </row>
-    <row r="72" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C72" s="118" t="s">
+      <c r="I68" s="64"/>
+      <c r="J68" s="63"/>
+      <c r="K68" s="64"/>
+      <c r="L68" s="66"/>
+    </row>
+    <row r="69" spans="3:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C69" s="63"/>
+      <c r="D69" s="66"/>
+      <c r="E69" s="66"/>
+      <c r="F69" s="66"/>
+      <c r="G69" s="66"/>
+      <c r="H69" s="66"/>
+      <c r="I69" s="64"/>
+      <c r="J69" s="63"/>
+      <c r="K69" s="64"/>
+      <c r="L69" s="66"/>
+    </row>
+    <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C70" s="63"/>
+      <c r="D70" s="66"/>
+      <c r="E70" s="66"/>
+      <c r="F70" s="66"/>
+      <c r="G70" s="66"/>
+      <c r="H70" s="66"/>
+      <c r="I70" s="64"/>
+      <c r="J70" s="63"/>
+      <c r="K70" s="64"/>
+      <c r="L70" s="66"/>
+    </row>
+    <row r="71" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C71" s="63"/>
+      <c r="D71" s="66"/>
+      <c r="E71" s="66"/>
+      <c r="F71" s="66"/>
+      <c r="G71" s="66"/>
+      <c r="H71" s="66"/>
+      <c r="I71" s="64"/>
+      <c r="J71" s="72"/>
+      <c r="K71" s="73"/>
+      <c r="L71" s="66"/>
+    </row>
+    <row r="72" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="D72" s="119"/>
-      <c r="E72" s="119"/>
-      <c r="F72" s="119"/>
-      <c r="G72" s="119"/>
-      <c r="H72" s="120">
+      <c r="D72" s="113"/>
+      <c r="E72" s="113"/>
+      <c r="F72" s="113"/>
+      <c r="G72" s="113"/>
+      <c r="H72" s="114">
         <f>SUM(H62:H71)</f>
         <v>116058.8285</v>
       </c>
-      <c r="I72" s="121"/>
-      <c r="J72" s="76"/>
-      <c r="K72" s="77"/>
-      <c r="L72" s="68"/>
-    </row>
-    <row r="75" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C76" s="125" t="s">
+      <c r="I72" s="115"/>
+      <c r="J72" s="74"/>
+      <c r="K72" s="75"/>
+      <c r="L72" s="66"/>
+    </row>
+    <row r="75" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C76" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="D76" s="126"/>
-      <c r="E76" s="126"/>
-      <c r="F76" s="126"/>
-      <c r="G76" s="126"/>
-      <c r="H76" s="126"/>
-      <c r="I76" s="121"/>
-      <c r="J76" s="63"/>
-      <c r="K76" s="64"/>
-      <c r="L76" s="68"/>
-    </row>
-    <row r="77" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C77" s="127" t="s">
+      <c r="D76" s="117"/>
+      <c r="E76" s="117"/>
+      <c r="F76" s="117"/>
+      <c r="G76" s="117"/>
+      <c r="H76" s="117"/>
+      <c r="I76" s="115"/>
+      <c r="J76" s="61"/>
+      <c r="K76" s="62"/>
+      <c r="L76" s="66"/>
+    </row>
+    <row r="77" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="D77" s="126"/>
-      <c r="E77" s="126"/>
-      <c r="F77" s="126"/>
-      <c r="G77" s="126"/>
-      <c r="H77" s="126"/>
-      <c r="I77" s="121"/>
-      <c r="J77" s="65"/>
-      <c r="K77" s="66"/>
-      <c r="L77" s="68"/>
-    </row>
-    <row r="78" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C78" s="63"/>
-      <c r="D78" s="67"/>
-      <c r="E78" s="67"/>
-      <c r="F78" s="67"/>
-      <c r="G78" s="68"/>
-      <c r="H78" s="68" t="s">
+      <c r="D77" s="117"/>
+      <c r="E77" s="117"/>
+      <c r="F77" s="117"/>
+      <c r="G77" s="117"/>
+      <c r="H77" s="117"/>
+      <c r="I77" s="115"/>
+      <c r="J77" s="63"/>
+      <c r="K77" s="64"/>
+      <c r="L77" s="66"/>
+    </row>
+    <row r="78" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C78" s="61"/>
+      <c r="D78" s="65"/>
+      <c r="E78" s="65"/>
+      <c r="F78" s="65"/>
+      <c r="G78" s="66"/>
+      <c r="H78" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="I78" s="66"/>
-      <c r="J78" s="65"/>
-      <c r="K78" s="66"/>
-      <c r="L78" s="68"/>
-    </row>
-    <row r="79" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C79" s="65" t="s">
+      <c r="I78" s="64"/>
+      <c r="J78" s="63"/>
+      <c r="K78" s="64"/>
+      <c r="L78" s="66"/>
+    </row>
+    <row r="79" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C79" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="D79" s="68"/>
-      <c r="E79" s="68"/>
-      <c r="F79" s="68"/>
-      <c r="G79" s="68"/>
-      <c r="H79" s="68" t="str">
+      <c r="D79" s="66"/>
+      <c r="E79" s="66"/>
+      <c r="F79" s="66"/>
+      <c r="G79" s="66"/>
+      <c r="H79" s="66" t="str">
         <f>H17</f>
         <v>VENCIMIENTO: DICIEMBRE</v>
       </c>
-      <c r="I79" s="66"/>
-      <c r="J79" s="65"/>
-      <c r="K79" s="66"/>
-      <c r="L79" s="68"/>
-    </row>
-    <row r="80" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C80" s="69"/>
-      <c r="D80" s="70"/>
-      <c r="E80" s="70"/>
-      <c r="F80" s="70"/>
-      <c r="G80" s="70"/>
-      <c r="H80" s="70"/>
-      <c r="I80" s="71"/>
-      <c r="J80" s="65"/>
-      <c r="K80" s="66"/>
-      <c r="L80" s="68"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C81" s="128" t="s">
+      <c r="I79" s="64"/>
+      <c r="J79" s="63"/>
+      <c r="K79" s="64"/>
+      <c r="L79" s="66"/>
+    </row>
+    <row r="80" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C80" s="67"/>
+      <c r="D80" s="68"/>
+      <c r="E80" s="68"/>
+      <c r="F80" s="68"/>
+      <c r="G80" s="68"/>
+      <c r="H80" s="68"/>
+      <c r="I80" s="69"/>
+      <c r="J80" s="63"/>
+      <c r="K80" s="64"/>
+      <c r="L80" s="66"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C81" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="D81" s="129"/>
-      <c r="E81" s="129"/>
-      <c r="F81" s="129"/>
-      <c r="G81" s="129"/>
-      <c r="H81" s="129"/>
-      <c r="I81" s="130"/>
-      <c r="J81" s="65"/>
-      <c r="K81" s="66"/>
-      <c r="L81" s="68"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C82" s="65"/>
-      <c r="D82" s="68"/>
-      <c r="E82" s="68"/>
-      <c r="F82" s="68"/>
-      <c r="G82" s="68"/>
-      <c r="H82" s="68"/>
-      <c r="I82" s="66"/>
-      <c r="J82" s="65"/>
-      <c r="K82" s="66"/>
-      <c r="L82" s="68"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C83" s="65" t="s">
+      <c r="D81" s="120"/>
+      <c r="E81" s="120"/>
+      <c r="F81" s="120"/>
+      <c r="G81" s="120"/>
+      <c r="H81" s="120"/>
+      <c r="I81" s="121"/>
+      <c r="J81" s="63"/>
+      <c r="K81" s="64"/>
+      <c r="L81" s="66"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C82" s="63"/>
+      <c r="D82" s="66"/>
+      <c r="E82" s="66"/>
+      <c r="F82" s="66"/>
+      <c r="G82" s="66"/>
+      <c r="H82" s="66"/>
+      <c r="I82" s="64"/>
+      <c r="J82" s="63"/>
+      <c r="K82" s="64"/>
+      <c r="L82" s="66"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C83" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="D83" s="68"/>
-      <c r="E83" s="68" t="str">
+      <c r="D83" s="66"/>
+      <c r="E83" s="66" t="str">
         <f>C8</f>
         <v xml:space="preserve">JOHANA </v>
       </c>
-      <c r="F83" s="68"/>
-      <c r="G83" s="68" t="s">
+      <c r="F83" s="66"/>
+      <c r="G83" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="H83" s="72"/>
-      <c r="I83" s="66"/>
-      <c r="J83" s="131" t="s">
+      <c r="H83" s="70"/>
+      <c r="I83" s="64"/>
+      <c r="J83" s="122" t="s">
         <v>53</v>
       </c>
-      <c r="K83" s="132"/>
-      <c r="L83" s="82"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C84" s="65" t="s">
+      <c r="K83" s="123"/>
+      <c r="L83" s="80"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C84" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="D84" s="73" t="s">
+      <c r="D84" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="E84" s="68">
+      <c r="E84" s="66">
         <f>A8</f>
         <v>4</v>
       </c>
-      <c r="F84" s="68"/>
-      <c r="G84" s="68"/>
-      <c r="H84" s="68"/>
-      <c r="I84" s="66"/>
-      <c r="J84" s="65"/>
-      <c r="K84" s="66"/>
-      <c r="L84" s="68"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C85" s="65"/>
-      <c r="D85" s="68"/>
-      <c r="E85" s="68"/>
-      <c r="F85" s="68"/>
-      <c r="G85" s="68"/>
-      <c r="H85" s="68"/>
-      <c r="I85" s="66"/>
-      <c r="J85" s="133"/>
-      <c r="K85" s="132"/>
-      <c r="L85" s="82"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C86" s="65" t="s">
+      <c r="F84" s="66"/>
+      <c r="G84" s="66"/>
+      <c r="H84" s="66"/>
+      <c r="I84" s="64"/>
+      <c r="J84" s="63"/>
+      <c r="K84" s="64"/>
+      <c r="L84" s="66"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C85" s="63"/>
+      <c r="D85" s="66"/>
+      <c r="E85" s="66"/>
+      <c r="F85" s="66"/>
+      <c r="G85" s="66"/>
+      <c r="H85" s="66"/>
+      <c r="I85" s="64"/>
+      <c r="J85" s="124"/>
+      <c r="K85" s="123"/>
+      <c r="L85" s="80"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C86" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="D86" s="68"/>
-      <c r="E86" s="68"/>
-      <c r="F86" s="68"/>
-      <c r="G86" s="68"/>
-      <c r="H86" s="78">
-        <f>M$1/5</f>
+      <c r="D86" s="66"/>
+      <c r="E86" s="66"/>
+      <c r="F86" s="66"/>
+      <c r="G86" s="66"/>
+      <c r="H86" s="76">
+        <f>L$1/5</f>
         <v>70692.445999999996</v>
       </c>
-      <c r="I86" s="66"/>
-      <c r="J86" s="65"/>
-      <c r="K86" s="66"/>
-      <c r="L86" s="68"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C87" s="80" t="s">
+      <c r="I86" s="64"/>
+      <c r="J86" s="63"/>
+      <c r="K86" s="64"/>
+      <c r="L86" s="66"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C87" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="68"/>
-      <c r="E87" s="68"/>
-      <c r="F87" s="68"/>
-      <c r="G87" s="68"/>
-      <c r="H87" s="78">
+      <c r="D87" s="66"/>
+      <c r="E87" s="66"/>
+      <c r="F87" s="66"/>
+      <c r="G87" s="66"/>
+      <c r="H87" s="76">
         <f>T$15/4</f>
         <v>24137.5</v>
       </c>
-      <c r="I87" s="66"/>
-      <c r="J87" s="65"/>
-      <c r="K87" s="66"/>
-      <c r="L87" s="68"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C88" s="80" t="s">
+      <c r="I87" s="64"/>
+      <c r="J87" s="63"/>
+      <c r="K87" s="64"/>
+      <c r="L87" s="66"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C88" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="D88" s="68"/>
-      <c r="E88" s="68"/>
-      <c r="F88" s="68"/>
-      <c r="G88" s="68"/>
-      <c r="H88" s="78">
+      <c r="D88" s="66"/>
+      <c r="E88" s="66"/>
+      <c r="F88" s="66"/>
+      <c r="G88" s="66"/>
+      <c r="H88" s="76">
         <f>T$16/4</f>
         <v>6997.9375</v>
       </c>
-      <c r="I88" s="66"/>
-      <c r="J88" s="65"/>
-      <c r="K88" s="66"/>
-      <c r="L88" s="68"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C89" s="80" t="s">
+      <c r="I88" s="64"/>
+      <c r="J88" s="63"/>
+      <c r="K88" s="64"/>
+      <c r="L88" s="66"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C89" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="D89" s="68"/>
-      <c r="E89" s="68"/>
-      <c r="F89" s="68"/>
-      <c r="G89" s="68"/>
-      <c r="H89" s="78">
+      <c r="D89" s="66"/>
+      <c r="E89" s="66"/>
+      <c r="F89" s="66"/>
+      <c r="G89" s="66"/>
+      <c r="H89" s="76">
         <f>T$17/4</f>
         <v>8000</v>
       </c>
-      <c r="I89" s="66"/>
-      <c r="J89" s="65"/>
-      <c r="K89" s="66"/>
-      <c r="L89" s="68"/>
-    </row>
-    <row r="90" spans="3:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C90" s="80" t="s">
+      <c r="I89" s="64"/>
+      <c r="J89" s="63"/>
+      <c r="K89" s="64"/>
+      <c r="L89" s="66"/>
+    </row>
+    <row r="90" spans="3:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C90" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="D90" s="68"/>
-      <c r="E90" s="68"/>
-      <c r="F90" s="68"/>
-      <c r="G90" s="68"/>
-      <c r="H90" s="78">
+      <c r="D90" s="66"/>
+      <c r="E90" s="66"/>
+      <c r="F90" s="66"/>
+      <c r="G90" s="66"/>
+      <c r="H90" s="76">
         <f>T$18/4</f>
         <v>6230.9449999999997</v>
       </c>
-      <c r="I90" s="66"/>
-      <c r="J90" s="65"/>
-      <c r="K90" s="66"/>
-      <c r="L90" s="68"/>
-    </row>
-    <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="D91" s="68"/>
-      <c r="E91" s="68"/>
-      <c r="F91" s="68"/>
-      <c r="G91" s="68"/>
-      <c r="H91" s="78"/>
-      <c r="I91" s="66"/>
-      <c r="J91" s="65"/>
-      <c r="K91" s="66"/>
-      <c r="L91" s="68"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C92" s="80" t="s">
+      <c r="I90" s="64"/>
+      <c r="J90" s="63"/>
+      <c r="K90" s="64"/>
+      <c r="L90" s="66"/>
+    </row>
+    <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D91" s="66"/>
+      <c r="E91" s="66"/>
+      <c r="F91" s="66"/>
+      <c r="G91" s="66"/>
+      <c r="H91" s="76"/>
+      <c r="I91" s="64"/>
+      <c r="J91" s="63"/>
+      <c r="K91" s="64"/>
+      <c r="L91" s="66"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C92" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="D92" s="68"/>
-      <c r="E92" s="68"/>
-      <c r="F92" s="68"/>
-      <c r="G92" s="68"/>
-      <c r="H92" s="78">
+      <c r="D92" s="66"/>
+      <c r="E92" s="66"/>
+      <c r="F92" s="66"/>
+      <c r="G92" s="66"/>
+      <c r="H92" s="76">
         <f>T$20/3</f>
         <v>0</v>
       </c>
-      <c r="I92" s="66"/>
-      <c r="J92" s="74"/>
-      <c r="K92" s="75"/>
-      <c r="L92" s="68"/>
-    </row>
-    <row r="93" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D93" s="68"/>
-      <c r="E93" s="68"/>
-      <c r="F93" s="68"/>
-      <c r="G93" s="68"/>
-      <c r="H93" s="68"/>
-      <c r="I93" s="66"/>
-      <c r="J93" s="65"/>
-      <c r="K93" s="66"/>
-      <c r="L93" s="68"/>
-    </row>
-    <row r="94" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C94" s="118" t="s">
+      <c r="I92" s="64"/>
+      <c r="J92" s="72"/>
+      <c r="K92" s="73"/>
+      <c r="L92" s="66"/>
+    </row>
+    <row r="93" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D93" s="66"/>
+      <c r="E93" s="66"/>
+      <c r="F93" s="66"/>
+      <c r="G93" s="66"/>
+      <c r="H93" s="66"/>
+      <c r="I93" s="64"/>
+      <c r="J93" s="63"/>
+      <c r="K93" s="64"/>
+      <c r="L93" s="66"/>
+    </row>
+    <row r="94" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C94" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="D94" s="119"/>
-      <c r="E94" s="119"/>
-      <c r="F94" s="119"/>
-      <c r="G94" s="119"/>
-      <c r="H94" s="120">
+      <c r="D94" s="113"/>
+      <c r="E94" s="113"/>
+      <c r="F94" s="113"/>
+      <c r="G94" s="113"/>
+      <c r="H94" s="114">
         <f>SUM(H86:H93)</f>
         <v>116058.8285</v>
       </c>
-      <c r="I94" s="121"/>
-      <c r="J94" s="76"/>
-      <c r="K94" s="77"/>
-      <c r="L94" s="68"/>
-    </row>
-    <row r="97" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="98" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C98" s="125" t="s">
+      <c r="I94" s="115"/>
+      <c r="J94" s="74"/>
+      <c r="K94" s="75"/>
+      <c r="L94" s="66"/>
+    </row>
+    <row r="97" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="98" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C98" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="D98" s="126"/>
-      <c r="E98" s="126"/>
-      <c r="F98" s="126"/>
-      <c r="G98" s="126"/>
-      <c r="H98" s="126"/>
-      <c r="I98" s="121"/>
-      <c r="J98" s="63"/>
-      <c r="K98" s="64"/>
-      <c r="L98" s="68"/>
-    </row>
-    <row r="99" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C99" s="127" t="s">
+      <c r="D98" s="117"/>
+      <c r="E98" s="117"/>
+      <c r="F98" s="117"/>
+      <c r="G98" s="117"/>
+      <c r="H98" s="117"/>
+      <c r="I98" s="115"/>
+      <c r="J98" s="61"/>
+      <c r="K98" s="62"/>
+      <c r="L98" s="66"/>
+    </row>
+    <row r="99" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C99" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="D99" s="126"/>
-      <c r="E99" s="126"/>
-      <c r="F99" s="126"/>
-      <c r="G99" s="126"/>
-      <c r="H99" s="126"/>
-      <c r="I99" s="121"/>
-      <c r="J99" s="65"/>
-      <c r="K99" s="66"/>
-      <c r="L99" s="68"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C100" s="63"/>
-      <c r="D100" s="67"/>
-      <c r="E100" s="67"/>
-      <c r="F100" s="67"/>
-      <c r="G100" s="68"/>
-      <c r="H100" s="68" t="s">
+      <c r="D99" s="117"/>
+      <c r="E99" s="117"/>
+      <c r="F99" s="117"/>
+      <c r="G99" s="117"/>
+      <c r="H99" s="117"/>
+      <c r="I99" s="115"/>
+      <c r="J99" s="63"/>
+      <c r="K99" s="64"/>
+      <c r="L99" s="66"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C100" s="61"/>
+      <c r="D100" s="65"/>
+      <c r="E100" s="65"/>
+      <c r="F100" s="65"/>
+      <c r="G100" s="66"/>
+      <c r="H100" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="I100" s="66"/>
-      <c r="J100" s="65"/>
-      <c r="K100" s="66"/>
-      <c r="L100" s="68"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C101" s="65" t="s">
+      <c r="I100" s="64"/>
+      <c r="J100" s="63"/>
+      <c r="K100" s="64"/>
+      <c r="L100" s="66"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C101" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="D101" s="68"/>
-      <c r="E101" s="68"/>
-      <c r="F101" s="68"/>
-      <c r="G101" s="68"/>
-      <c r="H101" s="68" t="str">
+      <c r="D101" s="66"/>
+      <c r="E101" s="66"/>
+      <c r="F101" s="66"/>
+      <c r="G101" s="66"/>
+      <c r="H101" s="66" t="str">
         <f>H17</f>
         <v>VENCIMIENTO: DICIEMBRE</v>
       </c>
-      <c r="I101" s="66"/>
-      <c r="J101" s="65"/>
-      <c r="K101" s="66"/>
-      <c r="L101" s="68"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C102" s="69"/>
-      <c r="D102" s="70"/>
-      <c r="E102" s="70"/>
-      <c r="F102" s="70"/>
-      <c r="G102" s="70"/>
-      <c r="H102" s="70"/>
-      <c r="I102" s="71"/>
-      <c r="J102" s="65"/>
-      <c r="K102" s="66"/>
-      <c r="L102" s="68"/>
-    </row>
-    <row r="103" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C103" s="128" t="s">
+      <c r="I101" s="64"/>
+      <c r="J101" s="63"/>
+      <c r="K101" s="64"/>
+      <c r="L101" s="66"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C102" s="67"/>
+      <c r="D102" s="68"/>
+      <c r="E102" s="68"/>
+      <c r="F102" s="68"/>
+      <c r="G102" s="68"/>
+      <c r="H102" s="68"/>
+      <c r="I102" s="69"/>
+      <c r="J102" s="63"/>
+      <c r="K102" s="64"/>
+      <c r="L102" s="66"/>
+    </row>
+    <row r="103" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C103" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="D103" s="129"/>
-      <c r="E103" s="129"/>
-      <c r="F103" s="129"/>
-      <c r="G103" s="129"/>
-      <c r="H103" s="129"/>
-      <c r="I103" s="130"/>
-      <c r="J103" s="65"/>
-      <c r="K103" s="66"/>
-      <c r="L103" s="68"/>
-    </row>
-    <row r="104" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C104" s="65"/>
-      <c r="D104" s="68"/>
-      <c r="E104" s="68"/>
-      <c r="F104" s="68"/>
-      <c r="G104" s="68"/>
-      <c r="H104" s="68"/>
-      <c r="I104" s="66"/>
-      <c r="J104" s="65"/>
-      <c r="K104" s="66"/>
-      <c r="L104" s="68"/>
-    </row>
-    <row r="105" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C105" s="65" t="s">
+      <c r="D103" s="120"/>
+      <c r="E103" s="120"/>
+      <c r="F103" s="120"/>
+      <c r="G103" s="120"/>
+      <c r="H103" s="120"/>
+      <c r="I103" s="121"/>
+      <c r="J103" s="63"/>
+      <c r="K103" s="64"/>
+      <c r="L103" s="66"/>
+    </row>
+    <row r="104" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C104" s="63"/>
+      <c r="D104" s="66"/>
+      <c r="E104" s="66"/>
+      <c r="F104" s="66"/>
+      <c r="G104" s="66"/>
+      <c r="H104" s="66"/>
+      <c r="I104" s="64"/>
+      <c r="J104" s="63"/>
+      <c r="K104" s="64"/>
+      <c r="L104" s="66"/>
+    </row>
+    <row r="105" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C105" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="D105" s="68"/>
-      <c r="E105" s="68" t="str">
+      <c r="D105" s="66"/>
+      <c r="E105" s="66" t="str">
         <f>C9</f>
         <v xml:space="preserve">VARLAS GUILLERMO </v>
       </c>
-      <c r="F105" s="68"/>
-      <c r="G105" s="68" t="s">
+      <c r="F105" s="66"/>
+      <c r="G105" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="H105" s="72"/>
-      <c r="I105" s="66"/>
-      <c r="J105" s="131" t="s">
+      <c r="H105" s="70"/>
+      <c r="I105" s="64"/>
+      <c r="J105" s="122" t="s">
         <v>53</v>
       </c>
-      <c r="K105" s="132"/>
-      <c r="L105" s="82"/>
-    </row>
-    <row r="106" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C106" s="65" t="s">
+      <c r="K105" s="123"/>
+      <c r="L105" s="80"/>
+    </row>
+    <row r="106" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C106" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="D106" s="73" t="s">
+      <c r="D106" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="E106" s="68">
+      <c r="E106" s="66">
         <v>5</v>
       </c>
-      <c r="F106" s="68"/>
-      <c r="G106" s="68"/>
-      <c r="H106" s="68"/>
-      <c r="I106" s="66"/>
-      <c r="J106" s="65"/>
-      <c r="K106" s="66"/>
-      <c r="L106" s="68"/>
-    </row>
-    <row r="107" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C107" s="65"/>
-      <c r="D107" s="68"/>
-      <c r="E107" s="68"/>
-      <c r="F107" s="68"/>
-      <c r="G107" s="68"/>
-      <c r="H107" s="68"/>
-      <c r="I107" s="66"/>
-      <c r="J107" s="133"/>
-      <c r="K107" s="132"/>
-      <c r="L107" s="82"/>
-    </row>
-    <row r="108" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C108" s="65" t="s">
+      <c r="F106" s="66"/>
+      <c r="G106" s="66"/>
+      <c r="H106" s="66"/>
+      <c r="I106" s="64"/>
+      <c r="J106" s="63"/>
+      <c r="K106" s="64"/>
+      <c r="L106" s="66"/>
+    </row>
+    <row r="107" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C107" s="63"/>
+      <c r="D107" s="66"/>
+      <c r="E107" s="66"/>
+      <c r="F107" s="66"/>
+      <c r="G107" s="66"/>
+      <c r="H107" s="66"/>
+      <c r="I107" s="64"/>
+      <c r="J107" s="124"/>
+      <c r="K107" s="123"/>
+      <c r="L107" s="80"/>
+    </row>
+    <row r="108" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C108" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="D108" s="68"/>
-      <c r="E108" s="68"/>
-      <c r="F108" s="68"/>
-      <c r="G108" s="68"/>
-      <c r="H108" s="78">
-        <f>M$1/5</f>
+      <c r="D108" s="66"/>
+      <c r="E108" s="66"/>
+      <c r="F108" s="66"/>
+      <c r="G108" s="66"/>
+      <c r="H108" s="76">
+        <f>L$1/5</f>
         <v>70692.445999999996</v>
       </c>
-      <c r="I108" s="66"/>
-      <c r="J108" s="65"/>
-      <c r="K108" s="66"/>
-      <c r="L108" s="68"/>
-    </row>
-    <row r="109" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C109" s="80" t="s">
+      <c r="I108" s="64"/>
+      <c r="J108" s="63"/>
+      <c r="K108" s="64"/>
+      <c r="L108" s="66"/>
+    </row>
+    <row r="109" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C109" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="D109" s="68"/>
-      <c r="E109" s="68"/>
-      <c r="F109" s="68"/>
-      <c r="G109" s="68"/>
-      <c r="H109" s="78">
+      <c r="D109" s="66"/>
+      <c r="E109" s="66"/>
+      <c r="F109" s="66"/>
+      <c r="G109" s="66"/>
+      <c r="H109" s="76">
         <f>T$15/4</f>
         <v>24137.5</v>
       </c>
-      <c r="I109" s="66"/>
-      <c r="J109" s="65"/>
-      <c r="K109" s="66"/>
-      <c r="L109" s="68"/>
-    </row>
-    <row r="110" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C110" s="80" t="s">
+      <c r="I109" s="64"/>
+      <c r="J109" s="63"/>
+      <c r="K109" s="64"/>
+      <c r="L109" s="66"/>
+    </row>
+    <row r="110" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C110" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="D110" s="68"/>
-      <c r="E110" s="68"/>
-      <c r="F110" s="68"/>
-      <c r="G110" s="68"/>
-      <c r="H110" s="78">
+      <c r="D110" s="66"/>
+      <c r="E110" s="66"/>
+      <c r="F110" s="66"/>
+      <c r="G110" s="66"/>
+      <c r="H110" s="76">
         <f>T$16/4</f>
         <v>6997.9375</v>
       </c>
-      <c r="I110" s="66"/>
-      <c r="J110" s="65"/>
-      <c r="K110" s="66"/>
-      <c r="L110" s="68"/>
-    </row>
-    <row r="111" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C111" s="80" t="s">
+      <c r="I110" s="64"/>
+      <c r="J110" s="63"/>
+      <c r="K110" s="64"/>
+      <c r="L110" s="66"/>
+    </row>
+    <row r="111" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C111" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="D111" s="68"/>
-      <c r="E111" s="68"/>
-      <c r="F111" s="68"/>
-      <c r="G111" s="68"/>
-      <c r="H111" s="78">
+      <c r="D111" s="66"/>
+      <c r="E111" s="66"/>
+      <c r="F111" s="66"/>
+      <c r="G111" s="66"/>
+      <c r="H111" s="76">
         <f>T$17/4</f>
         <v>8000</v>
       </c>
-      <c r="I111" s="66"/>
-      <c r="J111" s="65"/>
-      <c r="K111" s="66"/>
-      <c r="L111" s="68"/>
-    </row>
-    <row r="112" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C112" s="80" t="s">
+      <c r="I111" s="64"/>
+      <c r="J111" s="63"/>
+      <c r="K111" s="64"/>
+      <c r="L111" s="66"/>
+    </row>
+    <row r="112" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C112" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="D112" s="68"/>
-      <c r="E112" s="68"/>
-      <c r="F112" s="68"/>
-      <c r="G112" s="68"/>
-      <c r="H112" s="78">
+      <c r="D112" s="66"/>
+      <c r="E112" s="66"/>
+      <c r="F112" s="66"/>
+      <c r="G112" s="66"/>
+      <c r="H112" s="76">
         <f>T$18/4</f>
         <v>6230.9449999999997</v>
       </c>
-      <c r="I112" s="66"/>
-      <c r="J112" s="65"/>
-      <c r="K112" s="66"/>
-      <c r="L112" s="68"/>
-    </row>
-    <row r="113" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="D113" s="68"/>
-      <c r="E113" s="68"/>
-      <c r="F113" s="68"/>
-      <c r="G113" s="68"/>
-      <c r="H113" s="78"/>
-      <c r="I113" s="66"/>
-      <c r="J113" s="65"/>
-      <c r="K113" s="66"/>
-      <c r="L113" s="68"/>
-    </row>
-    <row r="114" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C114" s="80" t="s">
+      <c r="I112" s="64"/>
+      <c r="J112" s="63"/>
+      <c r="K112" s="64"/>
+      <c r="L112" s="66"/>
+    </row>
+    <row r="113" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D113" s="66"/>
+      <c r="E113" s="66"/>
+      <c r="F113" s="66"/>
+      <c r="G113" s="66"/>
+      <c r="H113" s="76"/>
+      <c r="I113" s="64"/>
+      <c r="J113" s="63"/>
+      <c r="K113" s="64"/>
+      <c r="L113" s="66"/>
+    </row>
+    <row r="114" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C114" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="D114" s="68"/>
-      <c r="E114" s="68"/>
-      <c r="F114" s="68"/>
-      <c r="G114" s="68"/>
-      <c r="H114" s="78">
+      <c r="D114" s="66"/>
+      <c r="E114" s="66"/>
+      <c r="F114" s="66"/>
+      <c r="G114" s="66"/>
+      <c r="H114" s="76">
         <f>T$20/3</f>
         <v>0</v>
       </c>
-      <c r="I114" s="66"/>
-      <c r="J114" s="74"/>
-      <c r="K114" s="75"/>
-      <c r="L114" s="68"/>
-    </row>
-    <row r="115" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D115" s="68"/>
-      <c r="E115" s="68"/>
-      <c r="F115" s="68"/>
-      <c r="G115" s="68"/>
-      <c r="H115" s="68"/>
-      <c r="I115" s="66"/>
-      <c r="J115" s="65"/>
-      <c r="K115" s="66"/>
-      <c r="L115" s="68"/>
-    </row>
-    <row r="116" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C116" s="118" t="s">
+      <c r="I114" s="64"/>
+      <c r="J114" s="72"/>
+      <c r="K114" s="73"/>
+      <c r="L114" s="66"/>
+    </row>
+    <row r="115" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D115" s="66"/>
+      <c r="E115" s="66"/>
+      <c r="F115" s="66"/>
+      <c r="G115" s="66"/>
+      <c r="H115" s="66"/>
+      <c r="I115" s="64"/>
+      <c r="J115" s="63"/>
+      <c r="K115" s="64"/>
+      <c r="L115" s="66"/>
+    </row>
+    <row r="116" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C116" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="D116" s="119"/>
-      <c r="E116" s="119"/>
-      <c r="F116" s="119"/>
-      <c r="G116" s="119"/>
-      <c r="H116" s="120">
+      <c r="D116" s="113"/>
+      <c r="E116" s="113"/>
+      <c r="F116" s="113"/>
+      <c r="G116" s="113"/>
+      <c r="H116" s="114">
         <f>SUM(H108:H115)</f>
         <v>116058.8285</v>
       </c>
-      <c r="I116" s="121"/>
-      <c r="J116" s="76"/>
-      <c r="K116" s="77"/>
-      <c r="L116" s="68"/>
+      <c r="I116" s="115"/>
+      <c r="J116" s="74"/>
+      <c r="K116" s="75"/>
+      <c r="L116" s="66"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="C52:I52"/>
-    <mergeCell ref="C53:I53"/>
-    <mergeCell ref="C57:I57"/>
+  <mergeCells count="39">
+    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="C116:G116"/>
+    <mergeCell ref="H116:I116"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C15:I15"/>
+    <mergeCell ref="C19:I19"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="C36:I36"/>
+    <mergeCell ref="C37:I37"/>
+    <mergeCell ref="C41:I41"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="J45:K45"/>
     <mergeCell ref="C49:G49"/>
     <mergeCell ref="H49:I49"/>
     <mergeCell ref="J105:K105"/>
@@ -3873,22 +3908,11 @@
     <mergeCell ref="C81:I81"/>
     <mergeCell ref="J83:K83"/>
     <mergeCell ref="J85:K85"/>
-    <mergeCell ref="C116:G116"/>
-    <mergeCell ref="H116:I116"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C15:I15"/>
-    <mergeCell ref="C19:I19"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="C36:I36"/>
-    <mergeCell ref="C37:I37"/>
-    <mergeCell ref="C41:I41"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="C52:I52"/>
+    <mergeCell ref="C53:I53"/>
+    <mergeCell ref="C57:I57"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/URIARTE 630/Mayo/EXPENSAS-MAYO.xlsx
+++ b/URIARTE 630/Mayo/EXPENSAS-MAYO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\URIARTE 630\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F97FB5-9351-45A6-A333-749F51CBBD01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05061FEC-0307-4DA1-8078-0E44E224C10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -230,9 +230,6 @@
     <t>SEGUNDO</t>
   </si>
   <si>
-    <t>ARBA cuota 2</t>
-  </si>
-  <si>
     <t>Vto. 16/06</t>
   </si>
   <si>
@@ -240,6 +237,9 @@
   </si>
   <si>
     <t xml:space="preserve">FERRETERIA V&amp;A </t>
+  </si>
+  <si>
+    <t>ARBA</t>
   </si>
 </sst>
 </file>
@@ -362,13 +362,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0" tint="-0.14999847407452621"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -417,12 +417,6 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="51">
     <border>
@@ -1028,7 +1022,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1153,7 +1147,6 @@
     <xf numFmtId="17" fontId="1" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="44" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1173,13 +1166,26 @@
     <xf numFmtId="164" fontId="1" fillId="3" borderId="46" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="46" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="3" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="47" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1187,6 +1193,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1204,31 +1219,8 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="47" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="10" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1640,10 +1632,10 @@
       <c r="C7" s="41"/>
       <c r="D7" s="41"/>
       <c r="E7" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F7" s="55" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1666,17 +1658,17 @@
       <c r="B11" s="19"/>
       <c r="C11" s="20"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="110" t="s">
+      <c r="E11" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="110"/>
+      <c r="F11" s="107"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="48" t="s">
         <v>43</v>
       </c>
       <c r="B12" s="48"/>
-      <c r="C12" s="108">
+      <c r="C12" s="130">
         <f>65200*5%+65200</f>
         <v>68460</v>
       </c>
@@ -1693,7 +1685,7 @@
         <v>44</v>
       </c>
       <c r="B13" s="48"/>
-      <c r="C13" s="108">
+      <c r="C13" s="130">
         <v>3567.21</v>
       </c>
       <c r="D13" s="4"/>
@@ -1705,8 +1697,8 @@
         <v>57</v>
       </c>
       <c r="B14" s="48"/>
-      <c r="C14" s="133">
-        <v>82851.100000000006</v>
+      <c r="C14" s="130">
+        <v>94499.520000000004</v>
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="33" t="s">
@@ -1719,10 +1711,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B15" s="48"/>
-      <c r="C15" s="109">
+      <c r="C15" s="46">
         <v>20000</v>
       </c>
       <c r="D15" s="24"/>
@@ -1734,7 +1726,7 @@
         <v>62</v>
       </c>
       <c r="B16" s="48"/>
-      <c r="C16" s="109">
+      <c r="C16" s="46">
         <v>109718</v>
       </c>
       <c r="D16" s="24"/>
@@ -1746,8 +1738,8 @@
         <v>38</v>
       </c>
       <c r="B17" s="57"/>
-      <c r="C17" s="133">
-        <v>13461.61</v>
+      <c r="C17" s="130">
+        <v>14102.85</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="33" t="s">
@@ -1755,7 +1747,7 @@
       </c>
       <c r="F17" s="34">
         <f>-C37 +C31</f>
-        <v>-472207.04</v>
+        <v>-484496.69999999995</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1763,7 +1755,7 @@
         <v>41</v>
       </c>
       <c r="B18" s="48"/>
-      <c r="C18" s="108">
+      <c r="C18" s="130">
         <v>32000</v>
       </c>
       <c r="D18" s="4"/>
@@ -1775,7 +1767,7 @@
         <v>39</v>
       </c>
       <c r="B19" s="56"/>
-      <c r="C19" s="108">
+      <c r="C19" s="130">
         <v>142149.12</v>
       </c>
       <c r="E19" s="33"/>
@@ -1783,11 +1775,11 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="56" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B20" s="48"/>
-      <c r="C20" s="133">
-        <v>9567.5</v>
+      <c r="C20" s="130">
+        <v>10470.799999999999</v>
       </c>
       <c r="E20" s="33"/>
       <c r="F20" s="34"/>
@@ -1797,7 +1789,7 @@
       <c r="B21" s="50"/>
       <c r="C21" s="81">
         <f>SUM(C12:C19)</f>
-        <v>472207.04</v>
+        <v>484496.69999999995</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="35" t="s">
@@ -1805,7 +1797,7 @@
       </c>
       <c r="F21" s="36">
         <f>SUM(F12:F19)</f>
-        <v>-804640.40107168001</v>
+        <v>-816930.06107167993</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1845,7 +1837,7 @@
       <c r="B25" s="27"/>
       <c r="C25" s="82">
         <f>+C24+C21</f>
-        <v>472207.04</v>
+        <v>484496.69999999995</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="12"/>
@@ -1894,8 +1886,8 @@
       <c r="F31" s="5"/>
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="111"/>
-      <c r="B32" s="111"/>
+      <c r="A32" s="108"/>
+      <c r="B32" s="108"/>
       <c r="C32" s="85"/>
       <c r="F32" s="5"/>
     </row>
@@ -1927,7 +1919,7 @@
       </c>
       <c r="C36" s="87">
         <f>C35+C25</f>
-        <v>472207.04</v>
+        <v>484496.69999999995</v>
       </c>
       <c r="F36" s="5"/>
     </row>
@@ -1938,7 +1930,7 @@
       <c r="B37" s="40"/>
       <c r="C37" s="54">
         <f>+C25+C34</f>
-        <v>472207.04</v>
+        <v>484496.69999999995</v>
       </c>
       <c r="E37" s="10"/>
     </row>
@@ -2039,28 +2031,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="125" t="str">
+      <c r="A1" s="118" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de MAYO</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
       <c r="D1" s="93"/>
       <c r="E1" s="94" t="s">
         <v>36</v>
       </c>
       <c r="F1" s="93"/>
-      <c r="G1" s="128" t="s">
+      <c r="G1" s="109" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
-      <c r="K1" s="130"/>
-      <c r="L1" s="131">
-        <v>353462.23</v>
-      </c>
-      <c r="M1" s="132"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="112">
+        <f>M2</f>
+        <v>484496.69999999995</v>
+      </c>
+      <c r="M1" s="113"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="95" t="str">
@@ -2080,10 +2073,12 @@
       <c r="J2" s="50"/>
       <c r="K2" s="81"/>
       <c r="L2" s="81"/>
-      <c r="M2" s="96"/>
+      <c r="M2" s="131">
+        <v>484496.69999999995</v>
+      </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="96" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -2119,12 +2114,12 @@
       <c r="L3" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="M3" s="98" t="s">
+      <c r="M3" s="97" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="97"/>
+      <c r="A4" s="96"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
         <v>42</v>
@@ -2155,12 +2150,12 @@
         <f>A2</f>
         <v>Vto. 16/06</v>
       </c>
-      <c r="M4" s="98" t="s">
+      <c r="M4" s="97" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="97">
+      <c r="A5" s="96">
         <v>1</v>
       </c>
       <c r="B5" s="7">
@@ -2192,7 +2187,7 @@
       </c>
       <c r="J5" s="23">
         <f>L$1*B5</f>
-        <v>74227.068299999999</v>
+        <v>101744.30699999999</v>
       </c>
       <c r="K5" s="9">
         <f>K$2*D5</f>
@@ -2200,15 +2195,15 @@
       </c>
       <c r="L5" s="9">
         <f>J5+K5+H5+G5</f>
-        <v>74227.068299999999</v>
-      </c>
-      <c r="M5" s="99">
+        <v>101744.30699999999</v>
+      </c>
+      <c r="M5" s="98">
         <f>L5+L5*4%</f>
-        <v>77196.151031999994</v>
+        <v>105814.07927999999</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="97">
+      <c r="A6" s="96">
         <v>2</v>
       </c>
       <c r="B6" s="7">
@@ -2237,7 +2232,7 @@
       </c>
       <c r="J6" s="23">
         <f>L$1*B6</f>
-        <v>56553.9568</v>
+        <v>77519.471999999994</v>
       </c>
       <c r="K6" s="9">
         <f>K$2*D6</f>
@@ -2245,15 +2240,15 @@
       </c>
       <c r="L6" s="9">
         <f t="shared" ref="L6:L9" si="2">J6+K6+H6+G6</f>
-        <v>118925.9533257216</v>
-      </c>
-      <c r="M6" s="99">
+        <v>139891.4685257216</v>
+      </c>
+      <c r="M6" s="98">
         <f t="shared" ref="M6:M9" si="3">L6+L6*4%</f>
-        <v>123682.99145875046</v>
+        <v>145487.12726675047</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="97">
+      <c r="A7" s="96">
         <v>3</v>
       </c>
       <c r="B7" s="7">
@@ -2278,22 +2273,22 @@
       <c r="I7" s="9"/>
       <c r="J7" s="23">
         <f>L$1*B7</f>
-        <v>74227.068299999999</v>
+        <v>101744.30699999999</v>
       </c>
       <c r="K7" s="9">
         <v>0</v>
       </c>
       <c r="L7" s="9">
         <f t="shared" si="2"/>
-        <v>296436.06474000961</v>
-      </c>
-      <c r="M7" s="99">
+        <v>323953.30344000959</v>
+      </c>
+      <c r="M7" s="98">
         <f t="shared" si="3"/>
-        <v>308293.50732961</v>
+        <v>336911.43557760998</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="97">
+      <c r="A8" s="96">
         <v>4</v>
       </c>
       <c r="B8" s="7">
@@ -2321,22 +2316,22 @@
       <c r="I8" s="9"/>
       <c r="J8" s="23">
         <f>L$1*B8</f>
-        <v>74227.068299999999</v>
+        <v>101744.30699999999</v>
       </c>
       <c r="K8" s="9">
         <v>0</v>
       </c>
       <c r="L8" s="9">
         <f t="shared" si="2"/>
-        <v>74227.068299999999</v>
-      </c>
-      <c r="M8" s="99">
+        <v>101744.30699999999</v>
+      </c>
+      <c r="M8" s="98">
         <f t="shared" si="3"/>
-        <v>77196.151031999994</v>
+        <v>105814.07927999999</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="97">
+      <c r="A9" s="96">
         <v>5</v>
       </c>
       <c r="B9" s="7">
@@ -2364,113 +2359,113 @@
       <c r="I9" s="9"/>
       <c r="J9" s="23">
         <f>L$1*B9</f>
-        <v>74227.068299999999</v>
+        <v>101744.30699999999</v>
       </c>
       <c r="K9" s="9">
         <v>0</v>
       </c>
       <c r="L9" s="9">
         <f t="shared" si="2"/>
-        <v>74227.068299999999</v>
-      </c>
-      <c r="M9" s="99">
+        <v>101744.30699999999</v>
+      </c>
+      <c r="M9" s="98">
         <f t="shared" si="3"/>
-        <v>77196.151031999994</v>
+        <v>105814.07927999999</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="100" t="s">
+      <c r="A10" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="101">
+      <c r="B10" s="100">
         <f>SUM(B5:B9)</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="C10" s="102"/>
-      <c r="D10" s="103">
+      <c r="C10" s="101"/>
+      <c r="D10" s="102">
         <f t="shared" ref="D10:K10" si="4">SUM(D5:D6)</f>
         <v>1</v>
       </c>
-      <c r="E10" s="104">
+      <c r="E10" s="103">
         <f>SUM(E5:E9)</f>
         <v>485209.79619679996</v>
       </c>
-      <c r="F10" s="104">
+      <c r="F10" s="103">
         <f>SUM(F5:F9)</f>
         <v>222681.20490000001</v>
       </c>
-      <c r="G10" s="104">
+      <c r="G10" s="103">
         <f t="shared" si="4"/>
         <v>57538.742182399998</v>
       </c>
-      <c r="H10" s="104">
+      <c r="H10" s="103">
         <f t="shared" si="4"/>
         <v>4833.2543433215997</v>
       </c>
-      <c r="I10" s="105">
+      <c r="I10" s="104">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J10" s="106">
+      <c r="J10" s="105">
         <f>SUM(J5:J9)</f>
-        <v>353462.23</v>
-      </c>
-      <c r="K10" s="106">
+        <v>484496.6999999999</v>
+      </c>
+      <c r="K10" s="105">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L10" s="104">
+      <c r="L10" s="103">
         <f>SUM(L5:L9)</f>
-        <v>638043.22296573129</v>
-      </c>
-      <c r="M10" s="107">
+        <v>769077.69296573126</v>
+      </c>
+      <c r="M10" s="106">
         <f>SUM(M5:M9)</f>
-        <v>663564.9518843604</v>
+        <v>799840.80068436032</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="127"/>
-      <c r="B11" s="127"/>
-      <c r="C11" s="127"/>
-      <c r="D11" s="127"/>
-      <c r="E11" s="127"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127"/>
-      <c r="J11" s="127"/>
-      <c r="K11" s="127"/>
-      <c r="L11" s="127"/>
-      <c r="M11" s="127"/>
+      <c r="A11" s="120"/>
+      <c r="B11" s="120"/>
+      <c r="C11" s="120"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="120"/>
+      <c r="F11" s="120"/>
+      <c r="G11" s="120"/>
+      <c r="H11" s="120"/>
+      <c r="I11" s="120"/>
+      <c r="J11" s="120"/>
+      <c r="K11" s="120"/>
+      <c r="L11" s="120"/>
+      <c r="M11" s="120"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M12" s="5"/>
     </row>
     <row r="13" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="116" t="s">
+      <c r="C14" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="117"/>
-      <c r="E14" s="117"/>
-      <c r="F14" s="117"/>
-      <c r="G14" s="117"/>
-      <c r="H14" s="117"/>
-      <c r="I14" s="115"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="117"/>
       <c r="J14" s="61"/>
       <c r="K14" s="62"/>
       <c r="L14" s="66"/>
     </row>
     <row r="15" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="118" t="s">
+      <c r="C15" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="117"/>
-      <c r="E15" s="117"/>
-      <c r="F15" s="117"/>
-      <c r="G15" s="117"/>
-      <c r="H15" s="117"/>
-      <c r="I15" s="115"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="117"/>
       <c r="J15" s="63"/>
       <c r="K15" s="64"/>
       <c r="L15" s="66"/>
@@ -2542,15 +2537,15 @@
       </c>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C19" s="119" t="s">
+      <c r="C19" s="124" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="120"/>
-      <c r="E19" s="120"/>
-      <c r="F19" s="120"/>
-      <c r="G19" s="120"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="121"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="125"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
+      <c r="I19" s="126"/>
       <c r="J19" s="63"/>
       <c r="K19" s="64"/>
       <c r="L19" s="66"/>
@@ -2588,10 +2583,10 @@
       </c>
       <c r="H21" s="70"/>
       <c r="I21" s="64"/>
-      <c r="J21" s="122" t="s">
+      <c r="J21" s="127" t="s">
         <v>53</v>
       </c>
-      <c r="K21" s="123"/>
+      <c r="K21" s="128"/>
       <c r="L21" s="80"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.25">
@@ -2621,8 +2616,8 @@
       <c r="G23" s="66"/>
       <c r="H23" s="66"/>
       <c r="I23" s="64"/>
-      <c r="J23" s="124"/>
-      <c r="K23" s="123"/>
+      <c r="J23" s="129"/>
+      <c r="K23" s="128"/>
       <c r="L23" s="80"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.25">
@@ -2635,7 +2630,7 @@
       <c r="G24" s="66"/>
       <c r="H24" s="76">
         <f>L$1/5</f>
-        <v>70692.445999999996</v>
+        <v>96899.34</v>
       </c>
       <c r="I24" s="64"/>
       <c r="J24" s="63"/>
@@ -2751,47 +2746,47 @@
       <c r="L31" s="66"/>
     </row>
     <row r="32" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="112" t="s">
+      <c r="C32" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="113"/>
-      <c r="E32" s="113"/>
-      <c r="F32" s="113"/>
-      <c r="G32" s="113"/>
-      <c r="H32" s="114">
+      <c r="D32" s="115"/>
+      <c r="E32" s="115"/>
+      <c r="F32" s="115"/>
+      <c r="G32" s="115"/>
+      <c r="H32" s="116">
         <f>SUM(H24:H31)</f>
-        <v>116058.8285</v>
-      </c>
-      <c r="I32" s="115"/>
+        <v>142265.7225</v>
+      </c>
+      <c r="I32" s="117"/>
       <c r="J32" s="74"/>
       <c r="K32" s="75"/>
       <c r="L32" s="66"/>
     </row>
     <row r="35" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="36" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="116" t="s">
+      <c r="C36" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="D36" s="117"/>
-      <c r="E36" s="117"/>
-      <c r="F36" s="117"/>
-      <c r="G36" s="117"/>
-      <c r="H36" s="117"/>
-      <c r="I36" s="115"/>
+      <c r="D36" s="122"/>
+      <c r="E36" s="122"/>
+      <c r="F36" s="122"/>
+      <c r="G36" s="122"/>
+      <c r="H36" s="122"/>
+      <c r="I36" s="117"/>
       <c r="J36" s="61"/>
       <c r="K36" s="62"/>
       <c r="L36" s="66"/>
     </row>
     <row r="37" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="118" t="s">
+      <c r="C37" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="D37" s="117"/>
-      <c r="E37" s="117"/>
-      <c r="F37" s="117"/>
-      <c r="G37" s="117"/>
-      <c r="H37" s="117"/>
-      <c r="I37" s="115"/>
+      <c r="D37" s="122"/>
+      <c r="E37" s="122"/>
+      <c r="F37" s="122"/>
+      <c r="G37" s="122"/>
+      <c r="H37" s="122"/>
+      <c r="I37" s="117"/>
       <c r="J37" s="63"/>
       <c r="K37" s="64"/>
       <c r="L37" s="66"/>
@@ -2840,15 +2835,15 @@
       <c r="L40" s="66"/>
     </row>
     <row r="41" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C41" s="119" t="s">
+      <c r="C41" s="124" t="s">
         <v>50</v>
       </c>
-      <c r="D41" s="120"/>
-      <c r="E41" s="120"/>
-      <c r="F41" s="120"/>
-      <c r="G41" s="120"/>
-      <c r="H41" s="120"/>
-      <c r="I41" s="121"/>
+      <c r="D41" s="125"/>
+      <c r="E41" s="125"/>
+      <c r="F41" s="125"/>
+      <c r="G41" s="125"/>
+      <c r="H41" s="125"/>
+      <c r="I41" s="126"/>
       <c r="J41" s="63"/>
       <c r="K41" s="64"/>
       <c r="L41" s="66"/>
@@ -2880,10 +2875,10 @@
       </c>
       <c r="H43" s="70"/>
       <c r="I43" s="64"/>
-      <c r="J43" s="122" t="s">
+      <c r="J43" s="127" t="s">
         <v>53</v>
       </c>
-      <c r="K43" s="123"/>
+      <c r="K43" s="128"/>
       <c r="L43" s="80"/>
     </row>
     <row r="44" spans="3:12" x14ac:dyDescent="0.25">
@@ -2913,8 +2908,8 @@
       <c r="G45" s="66"/>
       <c r="H45" s="66"/>
       <c r="I45" s="64"/>
-      <c r="J45" s="124"/>
-      <c r="K45" s="123"/>
+      <c r="J45" s="129"/>
+      <c r="K45" s="128"/>
       <c r="L45" s="80"/>
     </row>
     <row r="46" spans="3:12" x14ac:dyDescent="0.25">
@@ -2927,7 +2922,7 @@
       <c r="G46" s="66"/>
       <c r="H46" s="76">
         <f>L$1/5</f>
-        <v>70692.445999999996</v>
+        <v>96899.34</v>
       </c>
       <c r="I46" s="64"/>
       <c r="J46" s="63"/>
@@ -2959,47 +2954,47 @@
       <c r="L48" s="66"/>
     </row>
     <row r="49" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="112" t="s">
+      <c r="C49" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="D49" s="113"/>
-      <c r="E49" s="113"/>
-      <c r="F49" s="113"/>
-      <c r="G49" s="113"/>
-      <c r="H49" s="114">
+      <c r="D49" s="115"/>
+      <c r="E49" s="115"/>
+      <c r="F49" s="115"/>
+      <c r="G49" s="115"/>
+      <c r="H49" s="116">
         <f>M6</f>
-        <v>123682.99145875046</v>
-      </c>
-      <c r="I49" s="115"/>
+        <v>145487.12726675047</v>
+      </c>
+      <c r="I49" s="117"/>
       <c r="J49" s="74"/>
       <c r="K49" s="75"/>
       <c r="L49" s="66"/>
     </row>
     <row r="51" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="52" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="116" t="s">
+      <c r="C52" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="D52" s="117"/>
-      <c r="E52" s="117"/>
-      <c r="F52" s="117"/>
-      <c r="G52" s="117"/>
-      <c r="H52" s="117"/>
-      <c r="I52" s="115"/>
+      <c r="D52" s="122"/>
+      <c r="E52" s="122"/>
+      <c r="F52" s="122"/>
+      <c r="G52" s="122"/>
+      <c r="H52" s="122"/>
+      <c r="I52" s="117"/>
       <c r="J52" s="61"/>
       <c r="K52" s="62"/>
       <c r="L52" s="66"/>
     </row>
     <row r="53" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="118" t="s">
+      <c r="C53" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="D53" s="117"/>
-      <c r="E53" s="117"/>
-      <c r="F53" s="117"/>
-      <c r="G53" s="117"/>
-      <c r="H53" s="117"/>
-      <c r="I53" s="115"/>
+      <c r="D53" s="122"/>
+      <c r="E53" s="122"/>
+      <c r="F53" s="122"/>
+      <c r="G53" s="122"/>
+      <c r="H53" s="122"/>
+      <c r="I53" s="117"/>
       <c r="J53" s="63"/>
       <c r="K53" s="64"/>
       <c r="L53" s="66"/>
@@ -3048,15 +3043,15 @@
       <c r="L56" s="66"/>
     </row>
     <row r="57" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C57" s="119" t="s">
+      <c r="C57" s="124" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="120"/>
-      <c r="E57" s="120"/>
-      <c r="F57" s="120"/>
-      <c r="G57" s="120"/>
-      <c r="H57" s="120"/>
-      <c r="I57" s="121"/>
+      <c r="D57" s="125"/>
+      <c r="E57" s="125"/>
+      <c r="F57" s="125"/>
+      <c r="G57" s="125"/>
+      <c r="H57" s="125"/>
+      <c r="I57" s="126"/>
       <c r="J57" s="63"/>
       <c r="K57" s="64"/>
       <c r="L57" s="66"/>
@@ -3088,10 +3083,10 @@
       </c>
       <c r="H59" s="70"/>
       <c r="I59" s="64"/>
-      <c r="J59" s="122" t="s">
+      <c r="J59" s="127" t="s">
         <v>53</v>
       </c>
-      <c r="K59" s="123"/>
+      <c r="K59" s="128"/>
       <c r="L59" s="80"/>
     </row>
     <row r="60" spans="3:12" x14ac:dyDescent="0.25">
@@ -3121,8 +3116,8 @@
       <c r="G61" s="66"/>
       <c r="H61" s="66"/>
       <c r="I61" s="64"/>
-      <c r="J61" s="124"/>
-      <c r="K61" s="123"/>
+      <c r="J61" s="129"/>
+      <c r="K61" s="128"/>
       <c r="L61" s="80"/>
     </row>
     <row r="62" spans="3:12" x14ac:dyDescent="0.25">
@@ -3135,7 +3130,7 @@
       <c r="G62" s="66"/>
       <c r="H62" s="76">
         <f>L$1/5</f>
-        <v>70692.445999999996</v>
+        <v>96899.34</v>
       </c>
       <c r="I62" s="64"/>
       <c r="J62" s="63"/>
@@ -3275,47 +3270,47 @@
       <c r="L71" s="66"/>
     </row>
     <row r="72" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="112" t="s">
+      <c r="C72" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="D72" s="113"/>
-      <c r="E72" s="113"/>
-      <c r="F72" s="113"/>
-      <c r="G72" s="113"/>
-      <c r="H72" s="114">
+      <c r="D72" s="115"/>
+      <c r="E72" s="115"/>
+      <c r="F72" s="115"/>
+      <c r="G72" s="115"/>
+      <c r="H72" s="116">
         <f>SUM(H62:H71)</f>
-        <v>116058.8285</v>
-      </c>
-      <c r="I72" s="115"/>
+        <v>142265.7225</v>
+      </c>
+      <c r="I72" s="117"/>
       <c r="J72" s="74"/>
       <c r="K72" s="75"/>
       <c r="L72" s="66"/>
     </row>
     <row r="75" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="76" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C76" s="116" t="s">
+      <c r="C76" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="D76" s="117"/>
-      <c r="E76" s="117"/>
-      <c r="F76" s="117"/>
-      <c r="G76" s="117"/>
-      <c r="H76" s="117"/>
-      <c r="I76" s="115"/>
+      <c r="D76" s="122"/>
+      <c r="E76" s="122"/>
+      <c r="F76" s="122"/>
+      <c r="G76" s="122"/>
+      <c r="H76" s="122"/>
+      <c r="I76" s="117"/>
       <c r="J76" s="61"/>
       <c r="K76" s="62"/>
       <c r="L76" s="66"/>
     </row>
     <row r="77" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="118" t="s">
+      <c r="C77" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="D77" s="117"/>
-      <c r="E77" s="117"/>
-      <c r="F77" s="117"/>
-      <c r="G77" s="117"/>
-      <c r="H77" s="117"/>
-      <c r="I77" s="115"/>
+      <c r="D77" s="122"/>
+      <c r="E77" s="122"/>
+      <c r="F77" s="122"/>
+      <c r="G77" s="122"/>
+      <c r="H77" s="122"/>
+      <c r="I77" s="117"/>
       <c r="J77" s="63"/>
       <c r="K77" s="64"/>
       <c r="L77" s="66"/>
@@ -3364,15 +3359,15 @@
       <c r="L80" s="66"/>
     </row>
     <row r="81" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C81" s="119" t="s">
+      <c r="C81" s="124" t="s">
         <v>50</v>
       </c>
-      <c r="D81" s="120"/>
-      <c r="E81" s="120"/>
-      <c r="F81" s="120"/>
-      <c r="G81" s="120"/>
-      <c r="H81" s="120"/>
-      <c r="I81" s="121"/>
+      <c r="D81" s="125"/>
+      <c r="E81" s="125"/>
+      <c r="F81" s="125"/>
+      <c r="G81" s="125"/>
+      <c r="H81" s="125"/>
+      <c r="I81" s="126"/>
       <c r="J81" s="63"/>
       <c r="K81" s="64"/>
       <c r="L81" s="66"/>
@@ -3404,10 +3399,10 @@
       </c>
       <c r="H83" s="70"/>
       <c r="I83" s="64"/>
-      <c r="J83" s="122" t="s">
+      <c r="J83" s="127" t="s">
         <v>53</v>
       </c>
-      <c r="K83" s="123"/>
+      <c r="K83" s="128"/>
       <c r="L83" s="80"/>
     </row>
     <row r="84" spans="3:12" x14ac:dyDescent="0.25">
@@ -3437,8 +3432,8 @@
       <c r="G85" s="66"/>
       <c r="H85" s="66"/>
       <c r="I85" s="64"/>
-      <c r="J85" s="124"/>
-      <c r="K85" s="123"/>
+      <c r="J85" s="129"/>
+      <c r="K85" s="128"/>
       <c r="L85" s="80"/>
     </row>
     <row r="86" spans="3:12" x14ac:dyDescent="0.25">
@@ -3451,7 +3446,7 @@
       <c r="G86" s="66"/>
       <c r="H86" s="76">
         <f>L$1/5</f>
-        <v>70692.445999999996</v>
+        <v>96899.34</v>
       </c>
       <c r="I86" s="64"/>
       <c r="J86" s="63"/>
@@ -3566,47 +3561,47 @@
       <c r="L93" s="66"/>
     </row>
     <row r="94" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C94" s="112" t="s">
+      <c r="C94" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="D94" s="113"/>
-      <c r="E94" s="113"/>
-      <c r="F94" s="113"/>
-      <c r="G94" s="113"/>
-      <c r="H94" s="114">
+      <c r="D94" s="115"/>
+      <c r="E94" s="115"/>
+      <c r="F94" s="115"/>
+      <c r="G94" s="115"/>
+      <c r="H94" s="116">
         <f>SUM(H86:H93)</f>
-        <v>116058.8285</v>
-      </c>
-      <c r="I94" s="115"/>
+        <v>142265.7225</v>
+      </c>
+      <c r="I94" s="117"/>
       <c r="J94" s="74"/>
       <c r="K94" s="75"/>
       <c r="L94" s="66"/>
     </row>
     <row r="97" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="98" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C98" s="116" t="s">
+      <c r="C98" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="D98" s="117"/>
-      <c r="E98" s="117"/>
-      <c r="F98" s="117"/>
-      <c r="G98" s="117"/>
-      <c r="H98" s="117"/>
-      <c r="I98" s="115"/>
+      <c r="D98" s="122"/>
+      <c r="E98" s="122"/>
+      <c r="F98" s="122"/>
+      <c r="G98" s="122"/>
+      <c r="H98" s="122"/>
+      <c r="I98" s="117"/>
       <c r="J98" s="61"/>
       <c r="K98" s="62"/>
       <c r="L98" s="66"/>
     </row>
     <row r="99" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C99" s="118" t="s">
+      <c r="C99" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="D99" s="117"/>
-      <c r="E99" s="117"/>
-      <c r="F99" s="117"/>
-      <c r="G99" s="117"/>
-      <c r="H99" s="117"/>
-      <c r="I99" s="115"/>
+      <c r="D99" s="122"/>
+      <c r="E99" s="122"/>
+      <c r="F99" s="122"/>
+      <c r="G99" s="122"/>
+      <c r="H99" s="122"/>
+      <c r="I99" s="117"/>
       <c r="J99" s="63"/>
       <c r="K99" s="64"/>
       <c r="L99" s="66"/>
@@ -3655,15 +3650,15 @@
       <c r="L102" s="66"/>
     </row>
     <row r="103" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C103" s="119" t="s">
+      <c r="C103" s="124" t="s">
         <v>50</v>
       </c>
-      <c r="D103" s="120"/>
-      <c r="E103" s="120"/>
-      <c r="F103" s="120"/>
-      <c r="G103" s="120"/>
-      <c r="H103" s="120"/>
-      <c r="I103" s="121"/>
+      <c r="D103" s="125"/>
+      <c r="E103" s="125"/>
+      <c r="F103" s="125"/>
+      <c r="G103" s="125"/>
+      <c r="H103" s="125"/>
+      <c r="I103" s="126"/>
       <c r="J103" s="63"/>
       <c r="K103" s="64"/>
       <c r="L103" s="66"/>
@@ -3695,10 +3690,10 @@
       </c>
       <c r="H105" s="70"/>
       <c r="I105" s="64"/>
-      <c r="J105" s="122" t="s">
+      <c r="J105" s="127" t="s">
         <v>53</v>
       </c>
-      <c r="K105" s="123"/>
+      <c r="K105" s="128"/>
       <c r="L105" s="80"/>
     </row>
     <row r="106" spans="3:12" x14ac:dyDescent="0.25">
@@ -3727,8 +3722,8 @@
       <c r="G107" s="66"/>
       <c r="H107" s="66"/>
       <c r="I107" s="64"/>
-      <c r="J107" s="124"/>
-      <c r="K107" s="123"/>
+      <c r="J107" s="129"/>
+      <c r="K107" s="128"/>
       <c r="L107" s="80"/>
     </row>
     <row r="108" spans="3:12" x14ac:dyDescent="0.25">
@@ -3741,7 +3736,7 @@
       <c r="G108" s="66"/>
       <c r="H108" s="76">
         <f>L$1/5</f>
-        <v>70692.445999999996</v>
+        <v>96899.34</v>
       </c>
       <c r="I108" s="64"/>
       <c r="J108" s="63"/>
@@ -3856,24 +3851,47 @@
       <c r="L115" s="66"/>
     </row>
     <row r="116" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C116" s="112" t="s">
+      <c r="C116" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="D116" s="113"/>
-      <c r="E116" s="113"/>
-      <c r="F116" s="113"/>
-      <c r="G116" s="113"/>
-      <c r="H116" s="114">
+      <c r="D116" s="115"/>
+      <c r="E116" s="115"/>
+      <c r="F116" s="115"/>
+      <c r="G116" s="115"/>
+      <c r="H116" s="116">
         <f>SUM(H108:H115)</f>
-        <v>116058.8285</v>
-      </c>
-      <c r="I116" s="115"/>
+        <v>142265.7225</v>
+      </c>
+      <c r="I116" s="117"/>
       <c r="J116" s="74"/>
       <c r="K116" s="75"/>
       <c r="L116" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="J107:K107"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="H94:I94"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="C98:I98"/>
+    <mergeCell ref="C99:I99"/>
+    <mergeCell ref="C103:I103"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C77:I77"/>
+    <mergeCell ref="C81:I81"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="C52:I52"/>
+    <mergeCell ref="C53:I53"/>
+    <mergeCell ref="C57:I57"/>
     <mergeCell ref="G1:K1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="C116:G116"/>
@@ -3890,29 +3908,6 @@
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="C37:I37"/>
     <mergeCell ref="C41:I41"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="J107:K107"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="H94:I94"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="J61:K61"/>
-    <mergeCell ref="C98:I98"/>
-    <mergeCell ref="C99:I99"/>
-    <mergeCell ref="C103:I103"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C77:I77"/>
-    <mergeCell ref="C81:I81"/>
-    <mergeCell ref="J83:K83"/>
-    <mergeCell ref="J85:K85"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="C52:I52"/>
-    <mergeCell ref="C53:I53"/>
-    <mergeCell ref="C57:I57"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
